--- a/main/all-profiles.xlsx
+++ b/main/all-profiles.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11146" uniqueCount="1001">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12922" uniqueCount="1087">
   <si>
     <t>Property</t>
   </si>
@@ -3108,6 +3108,270 @@
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/identity-assuranceLevel|4.0.1</t>
+  </si>
+  <si>
+    <t>match-parameters-profile</t>
+  </si>
+  <si>
+    <t>https://ths-greifswald.de/fhir/StructureDefinition/epix/MatchParametersProfile</t>
+  </si>
+  <si>
+    <t>MatchParametersProfile</t>
+  </si>
+  <si>
+    <t>Match Parameters Profile</t>
+  </si>
+  <si>
+    <t>Match informationen zu zwei Identitäten inklusive der betroffenden Identitäten, Score, MatchResult und LinkId des Matches</t>
+  </si>
+  <si>
+    <t>Parameters</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/StructureDefinition/Parameters</t>
+  </si>
+  <si>
+    <t>Match Informationen zu zwei Identitäten</t>
+  </si>
+  <si>
+    <t>This resource is a non-persisted resource used to pass information into and back from an [operation](http://hl7.org/fhir/R4/operations.html). It has no other use, and there is no RESTful endpoint associated with it.</t>
+  </si>
+  <si>
+    <t>Parameters.id</t>
+  </si>
+  <si>
+    <t>Parameters.meta</t>
+  </si>
+  <si>
+    <t>Parameters.meta.id</t>
+  </si>
+  <si>
+    <t>Parameters.meta.extension</t>
+  </si>
+  <si>
+    <t>Parameters.meta.versionId</t>
+  </si>
+  <si>
+    <t>Parameters.meta.lastUpdated</t>
+  </si>
+  <si>
+    <t>Parameters.meta.source</t>
+  </si>
+  <si>
+    <t>Parameters.meta.profile</t>
+  </si>
+  <si>
+    <t>Parameters.meta.security</t>
+  </si>
+  <si>
+    <t>Parameters.meta.tag</t>
+  </si>
+  <si>
+    <t>Parameters.implicitRules</t>
+  </si>
+  <si>
+    <t>Parameters.language</t>
+  </si>
+  <si>
+    <t>Parameters.parameter</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>Operation Parameter</t>
+  </si>
+  <si>
+    <t>A parameter passed to or received from the operation.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:name}
+</t>
+  </si>
+  <si>
+    <t>closed</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+inv-1:A parameter must have one and only one of (value, resource, part) {(part.exists() and value.empty() and resource.empty()) or (part.empty() and (value.exists() xor resource.exists()))}</t>
+  </si>
+  <si>
+    <t>Parameters.parameter.id</t>
+  </si>
+  <si>
+    <t>Parameters.parameter.extension</t>
+  </si>
+  <si>
+    <t>Parameters.parameter.modifierExtension</t>
+  </si>
+  <si>
+    <t>Parameters.parameter.name</t>
+  </si>
+  <si>
+    <t>Name from the definition</t>
+  </si>
+  <si>
+    <t>The name of the parameter (reference to the operation definition).</t>
+  </si>
+  <si>
+    <t>Parameters.parameter.value[x]</t>
+  </si>
+  <si>
+    <t>If parameter is a data type</t>
+  </si>
+  <si>
+    <t>If the parameter is a data type.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">inv-1
+</t>
+  </si>
+  <si>
+    <t>Parameters.parameter.resource</t>
+  </si>
+  <si>
+    <t>If parameter is a whole resource</t>
+  </si>
+  <si>
+    <t>If the parameter is a whole resource.</t>
+  </si>
+  <si>
+    <t>When resolving references in resources, the operation definition may specify how references may be resolved between parameters. If a reference cannot be resolved between the parameters, the application should fall back to it's general resource resolution methods.</t>
+  </si>
+  <si>
+    <t>Parameters.parameter.part</t>
+  </si>
+  <si>
+    <t>Named part of a multi-part parameter</t>
+  </si>
+  <si>
+    <t>A named part of a multi-part parameter.</t>
+  </si>
+  <si>
+    <t>Only one level of nested parameters is allowed.</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:matchItem</t>
+  </si>
+  <si>
+    <t>matchItem</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:matchItem.id</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:matchItem.extension</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:matchItem.modifierExtension</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:matchItem.name</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:matchItem.value[x]</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:matchItem.resource</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Patient
+</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:matchItem.part</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:matchScore</t>
+  </si>
+  <si>
+    <t>matchScore</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:matchScore.id</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:matchScore.extension</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:matchScore.modifierExtension</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:matchScore.name</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:matchScore.value[x]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">decimal
+</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:matchScore.resource</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:matchScore.part</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:matchResult</t>
+  </si>
+  <si>
+    <t>matchResult</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:matchResult.id</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:matchResult.extension</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:matchResult.modifierExtension</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:matchResult.name</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:matchResult.value[x]</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:matchResult.resource</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:matchResult.part</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:linkId</t>
+  </si>
+  <si>
+    <t>linkId</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:linkId.id</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:linkId.extension</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:linkId.modifierExtension</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:linkId.name</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:linkId.value[x]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">integer
+</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:linkId.resource</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:linkId.part</t>
   </si>
 </sst>
 </file>
@@ -3241,7 +3505,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B65"/>
+  <dimension ref="A1:B86"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="15.703125" customWidth="true"/>
@@ -3762,6 +4026,172 @@
         <v>38</v>
       </c>
     </row>
+    <row r="66">
+      <c r="A66" t="s" s="1">
+        <v>0</v>
+      </c>
+      <c r="B66" t="s" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s" s="2">
+        <v>2</v>
+      </c>
+      <c r="B67" t="s" s="2">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s" s="2">
+        <v>4</v>
+      </c>
+      <c r="B68" t="s" s="2">
+        <v>1002</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="B69" t="s" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s" s="2">
+        <v>8</v>
+      </c>
+      <c r="B70" t="s" s="2">
+        <v>1003</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s" s="2">
+        <v>9</v>
+      </c>
+      <c r="B71" t="s" s="2">
+        <v>1004</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s" s="2">
+        <v>11</v>
+      </c>
+      <c r="B72" t="s" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B73" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="B74" t="s" s="2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="B75" t="s" s="2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="B76" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B77" t="s" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="B78" t="s" s="2">
+        <v>1005</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="B79" s="2"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="s" s="2">
+        <v>26</v>
+      </c>
+      <c r="B80" t="s" s="2">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s" s="2">
+        <v>28</v>
+      </c>
+      <c r="B81" t="s" s="2">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="B82" t="s" s="2">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="B83" t="s" s="2">
+        <v>1006</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="B84" t="s" s="2">
+        <v>1007</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B85" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="B86" t="s" s="2">
+        <v>38</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
@@ -3769,10 +4199,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK334"/>
+  <dimension ref="A1:AK387"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="15.21484375" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="21.1171875" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="59.46484375" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="46.26171875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="14.98046875" customWidth="true" bestFit="true" hidden="true"/>
@@ -3791,7 +4221,7 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="7.6953125" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="10.79296875" customWidth="true" bestFit="true"/>
     <col min="21" max="21" width="34.26953125" customWidth="true" bestFit="true"/>
     <col min="22" max="22" width="14.72265625" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="15.13671875" customWidth="true" bestFit="true"/>
@@ -38803,6 +39233,5543 @@
         <v>121</v>
       </c>
     </row>
+    <row r="335">
+      <c r="A335" t="s" s="2">
+        <v>1001</v>
+      </c>
+      <c r="B335" t="s" s="2">
+        <v>1006</v>
+      </c>
+      <c r="C335" t="s" s="2">
+        <v>1006</v>
+      </c>
+      <c r="D335" s="2"/>
+      <c r="E335" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="F335" s="2"/>
+      <c r="G335" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H335" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I335" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="J335" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="K335" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="L335" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="M335" t="s" s="2">
+        <v>1008</v>
+      </c>
+      <c r="N335" t="s" s="2">
+        <v>1009</v>
+      </c>
+      <c r="O335" t="s" s="2">
+        <v>1008</v>
+      </c>
+      <c r="P335" s="2"/>
+      <c r="Q335" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="R335" s="2"/>
+      <c r="S335" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="T335" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="U335" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="V335" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="W335" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="X335" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Y335" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Z335" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AA335" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AB335" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AC335" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AD335" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AE335" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AF335" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AG335" t="s" s="2">
+        <v>1006</v>
+      </c>
+      <c r="AH335" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI335" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ335" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AK335" t="s" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="s" s="2">
+        <v>1001</v>
+      </c>
+      <c r="B336" t="s" s="2">
+        <v>1010</v>
+      </c>
+      <c r="C336" t="s" s="2">
+        <v>1010</v>
+      </c>
+      <c r="D336" s="2"/>
+      <c r="E336" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="F336" s="2"/>
+      <c r="G336" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H336" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I336" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="J336" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="K336" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L336" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="M336" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="N336" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="O336" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="P336" s="2"/>
+      <c r="Q336" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="R336" s="2"/>
+      <c r="S336" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="T336" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="U336" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="V336" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="W336" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="X336" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Y336" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Z336" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AA336" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AB336" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AC336" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AD336" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AE336" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AF336" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AG336" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="AH336" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI336" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ336" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AK336" t="s" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="s" s="2">
+        <v>1001</v>
+      </c>
+      <c r="B337" t="s" s="2">
+        <v>1011</v>
+      </c>
+      <c r="C337" t="s" s="2">
+        <v>1011</v>
+      </c>
+      <c r="D337" s="2"/>
+      <c r="E337" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="F337" s="2"/>
+      <c r="G337" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H337" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I337" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="J337" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="K337" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L337" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="M337" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="N337" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="O337" s="2"/>
+      <c r="P337" s="2"/>
+      <c r="Q337" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="R337" s="2"/>
+      <c r="S337" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="T337" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="U337" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="V337" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="W337" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="X337" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Y337" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Z337" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AA337" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AB337" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AC337" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AD337" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AE337" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AF337" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AG337" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="AH337" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI337" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ337" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AK337" t="s" s="2">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="s" s="2">
+        <v>1001</v>
+      </c>
+      <c r="B338" t="s" s="2">
+        <v>1012</v>
+      </c>
+      <c r="C338" t="s" s="2">
+        <v>1012</v>
+      </c>
+      <c r="D338" s="2"/>
+      <c r="E338" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="F338" s="2"/>
+      <c r="G338" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H338" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I338" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="J338" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="K338" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="L338" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="M338" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="N338" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="O338" s="2"/>
+      <c r="P338" s="2"/>
+      <c r="Q338" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="R338" s="2"/>
+      <c r="S338" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="T338" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="U338" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="V338" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="W338" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="X338" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Y338" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Z338" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AA338" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AB338" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AC338" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AD338" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AE338" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AF338" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AG338" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AH338" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI338" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ338" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AK338" t="s" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="s" s="2">
+        <v>1001</v>
+      </c>
+      <c r="B339" t="s" s="2">
+        <v>1013</v>
+      </c>
+      <c r="C339" t="s" s="2">
+        <v>1013</v>
+      </c>
+      <c r="D339" s="2"/>
+      <c r="E339" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="F339" s="2"/>
+      <c r="G339" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H339" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I339" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="J339" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="K339" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="L339" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="M339" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="N339" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="O339" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="P339" s="2"/>
+      <c r="Q339" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="R339" s="2"/>
+      <c r="S339" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="T339" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="U339" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="V339" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="W339" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="X339" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Y339" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Z339" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AA339" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AB339" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AC339" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AD339" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AE339" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AF339" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AG339" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AH339" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI339" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ339" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AK339" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="s" s="2">
+        <v>1001</v>
+      </c>
+      <c r="B340" t="s" s="2">
+        <v>1014</v>
+      </c>
+      <c r="C340" t="s" s="2">
+        <v>1014</v>
+      </c>
+      <c r="D340" s="2"/>
+      <c r="E340" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="F340" s="2"/>
+      <c r="G340" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H340" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I340" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="J340" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="K340" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L340" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="M340" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="N340" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="O340" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="P340" s="2"/>
+      <c r="Q340" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="R340" s="2"/>
+      <c r="S340" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="T340" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="U340" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="V340" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="W340" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="X340" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Y340" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Z340" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AA340" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AB340" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AC340" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AD340" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AE340" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AF340" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AG340" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="AH340" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI340" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ340" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AK340" t="s" s="2">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="s" s="2">
+        <v>1001</v>
+      </c>
+      <c r="B341" t="s" s="2">
+        <v>1015</v>
+      </c>
+      <c r="C341" t="s" s="2">
+        <v>1015</v>
+      </c>
+      <c r="D341" s="2"/>
+      <c r="E341" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="F341" s="2"/>
+      <c r="G341" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H341" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I341" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="J341" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="K341" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L341" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="M341" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="N341" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="O341" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="P341" s="2"/>
+      <c r="Q341" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="R341" s="2"/>
+      <c r="S341" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="T341" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="U341" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="V341" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="W341" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="X341" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Y341" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Z341" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AA341" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AB341" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AC341" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AD341" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AE341" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AF341" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AG341" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="AH341" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI341" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ341" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AK341" t="s" s="2">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="s" s="2">
+        <v>1001</v>
+      </c>
+      <c r="B342" t="s" s="2">
+        <v>1016</v>
+      </c>
+      <c r="C342" t="s" s="2">
+        <v>1016</v>
+      </c>
+      <c r="D342" s="2"/>
+      <c r="E342" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="F342" s="2"/>
+      <c r="G342" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H342" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I342" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="J342" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="K342" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L342" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="M342" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="N342" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="O342" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="P342" s="2"/>
+      <c r="Q342" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="R342" s="2"/>
+      <c r="S342" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="T342" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="U342" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="V342" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="W342" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="X342" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Y342" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Z342" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AA342" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AB342" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AC342" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AD342" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AE342" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AF342" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AG342" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="AH342" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI342" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ342" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AK342" t="s" s="2">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="s" s="2">
+        <v>1001</v>
+      </c>
+      <c r="B343" t="s" s="2">
+        <v>1017</v>
+      </c>
+      <c r="C343" t="s" s="2">
+        <v>1017</v>
+      </c>
+      <c r="D343" s="2"/>
+      <c r="E343" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="F343" s="2"/>
+      <c r="G343" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H343" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I343" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="J343" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="K343" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L343" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="M343" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="N343" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="O343" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="P343" s="2"/>
+      <c r="Q343" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="R343" s="2"/>
+      <c r="S343" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="T343" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="U343" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="V343" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="W343" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="X343" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Y343" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Z343" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AA343" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AB343" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AC343" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AD343" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AE343" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AF343" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AG343" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="AH343" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI343" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ343" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AK343" t="s" s="2">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="s" s="2">
+        <v>1001</v>
+      </c>
+      <c r="B344" t="s" s="2">
+        <v>1018</v>
+      </c>
+      <c r="C344" t="s" s="2">
+        <v>1018</v>
+      </c>
+      <c r="D344" s="2"/>
+      <c r="E344" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="F344" s="2"/>
+      <c r="G344" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H344" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I344" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="J344" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="K344" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L344" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="M344" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="N344" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="O344" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="P344" s="2"/>
+      <c r="Q344" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="R344" s="2"/>
+      <c r="S344" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="T344" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="U344" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="V344" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="W344" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="X344" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Y344" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="Z344" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="AA344" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="AB344" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AC344" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AD344" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AE344" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AF344" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AG344" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="AH344" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI344" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ344" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AK344" t="s" s="2">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="s" s="2">
+        <v>1001</v>
+      </c>
+      <c r="B345" t="s" s="2">
+        <v>1019</v>
+      </c>
+      <c r="C345" t="s" s="2">
+        <v>1019</v>
+      </c>
+      <c r="D345" s="2"/>
+      <c r="E345" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="F345" s="2"/>
+      <c r="G345" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H345" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I345" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="J345" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="K345" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L345" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="M345" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="N345" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="O345" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="P345" s="2"/>
+      <c r="Q345" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="R345" s="2"/>
+      <c r="S345" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="T345" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="U345" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="V345" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="W345" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="X345" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Y345" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="Z345" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="AA345" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="AB345" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AC345" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AD345" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AE345" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AF345" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AG345" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="AH345" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI345" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ345" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AK345" t="s" s="2">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="s" s="2">
+        <v>1001</v>
+      </c>
+      <c r="B346" t="s" s="2">
+        <v>1020</v>
+      </c>
+      <c r="C346" t="s" s="2">
+        <v>1020</v>
+      </c>
+      <c r="D346" s="2"/>
+      <c r="E346" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="F346" s="2"/>
+      <c r="G346" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H346" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I346" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="J346" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="K346" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L346" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="M346" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="N346" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="O346" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="P346" s="2"/>
+      <c r="Q346" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="R346" s="2"/>
+      <c r="S346" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="T346" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="U346" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="V346" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="W346" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="X346" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Y346" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Z346" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AA346" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AB346" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AC346" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AD346" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AE346" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AF346" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AG346" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="AH346" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI346" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ346" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AK346" t="s" s="2">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="s" s="2">
+        <v>1001</v>
+      </c>
+      <c r="B347" t="s" s="2">
+        <v>1021</v>
+      </c>
+      <c r="C347" t="s" s="2">
+        <v>1021</v>
+      </c>
+      <c r="D347" s="2"/>
+      <c r="E347" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="F347" s="2"/>
+      <c r="G347" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H347" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I347" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="J347" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="K347" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="L347" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="M347" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="N347" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="O347" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="P347" s="2"/>
+      <c r="Q347" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="R347" s="2"/>
+      <c r="S347" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="T347" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="U347" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="V347" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="W347" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="X347" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Y347" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="Z347" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="AA347" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="AB347" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AC347" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AD347" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AE347" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AF347" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AG347" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="AH347" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI347" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ347" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AK347" t="s" s="2">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="s" s="2">
+        <v>1001</v>
+      </c>
+      <c r="B348" t="s" s="2">
+        <v>1022</v>
+      </c>
+      <c r="C348" t="s" s="2">
+        <v>1022</v>
+      </c>
+      <c r="D348" s="2"/>
+      <c r="E348" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="F348" s="2"/>
+      <c r="G348" t="s" s="2">
+        <v>1023</v>
+      </c>
+      <c r="H348" t="s" s="2">
+        <v>1023</v>
+      </c>
+      <c r="I348" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="J348" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="K348" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L348" t="s" s="2">
+        <v>722</v>
+      </c>
+      <c r="M348" t="s" s="2">
+        <v>1024</v>
+      </c>
+      <c r="N348" t="s" s="2">
+        <v>1025</v>
+      </c>
+      <c r="O348" s="2"/>
+      <c r="P348" s="2"/>
+      <c r="Q348" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="R348" s="2"/>
+      <c r="S348" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="T348" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="U348" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="V348" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="W348" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="X348" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Y348" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Z348" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AA348" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AB348" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AC348" t="s" s="2">
+        <v>1026</v>
+      </c>
+      <c r="AD348" s="2"/>
+      <c r="AE348" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AF348" t="s" s="2">
+        <v>1027</v>
+      </c>
+      <c r="AG348" t="s" s="2">
+        <v>1022</v>
+      </c>
+      <c r="AH348" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI348" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ348" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AK348" t="s" s="2">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="s" s="2">
+        <v>1001</v>
+      </c>
+      <c r="B349" t="s" s="2">
+        <v>1029</v>
+      </c>
+      <c r="C349" t="s" s="2">
+        <v>1029</v>
+      </c>
+      <c r="D349" s="2"/>
+      <c r="E349" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="F349" s="2"/>
+      <c r="G349" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H349" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I349" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="J349" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="K349" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="L349" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="M349" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="N349" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="O349" s="2"/>
+      <c r="P349" s="2"/>
+      <c r="Q349" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="R349" s="2"/>
+      <c r="S349" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="T349" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="U349" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="V349" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="W349" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="X349" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Y349" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Z349" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AA349" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AB349" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AC349" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AD349" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AE349" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AF349" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AG349" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AH349" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI349" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ349" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AK349" t="s" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="s" s="2">
+        <v>1001</v>
+      </c>
+      <c r="B350" t="s" s="2">
+        <v>1030</v>
+      </c>
+      <c r="C350" t="s" s="2">
+        <v>1030</v>
+      </c>
+      <c r="D350" s="2"/>
+      <c r="E350" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="F350" s="2"/>
+      <c r="G350" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H350" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I350" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="J350" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="K350" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="L350" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="M350" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="N350" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="O350" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="P350" s="2"/>
+      <c r="Q350" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="R350" s="2"/>
+      <c r="S350" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="T350" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="U350" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="V350" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="W350" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="X350" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Y350" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Z350" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AA350" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AB350" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AC350" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AD350" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AE350" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AF350" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AG350" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AH350" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI350" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ350" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AK350" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="s" s="2">
+        <v>1001</v>
+      </c>
+      <c r="B351" t="s" s="2">
+        <v>1031</v>
+      </c>
+      <c r="C351" t="s" s="2">
+        <v>1031</v>
+      </c>
+      <c r="D351" s="2"/>
+      <c r="E351" t="s" s="2">
+        <v>731</v>
+      </c>
+      <c r="F351" s="2"/>
+      <c r="G351" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H351" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I351" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="J351" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="K351" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L351" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="M351" t="s" s="2">
+        <v>732</v>
+      </c>
+      <c r="N351" t="s" s="2">
+        <v>733</v>
+      </c>
+      <c r="O351" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="P351" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="Q351" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="R351" s="2"/>
+      <c r="S351" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="T351" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="U351" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="V351" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="W351" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="X351" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Y351" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Z351" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AA351" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AB351" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AC351" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AD351" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AE351" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AF351" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AG351" t="s" s="2">
+        <v>734</v>
+      </c>
+      <c r="AH351" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI351" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ351" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AK351" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="s" s="2">
+        <v>1001</v>
+      </c>
+      <c r="B352" t="s" s="2">
+        <v>1032</v>
+      </c>
+      <c r="C352" t="s" s="2">
+        <v>1032</v>
+      </c>
+      <c r="D352" s="2"/>
+      <c r="E352" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="F352" s="2"/>
+      <c r="G352" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H352" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I352" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="J352" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="K352" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L352" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="M352" t="s" s="2">
+        <v>1033</v>
+      </c>
+      <c r="N352" t="s" s="2">
+        <v>1034</v>
+      </c>
+      <c r="O352" s="2"/>
+      <c r="P352" s="2"/>
+      <c r="Q352" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="R352" s="2"/>
+      <c r="S352" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="T352" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="U352" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="V352" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="W352" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="X352" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Y352" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Z352" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AA352" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AB352" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AC352" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AD352" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AE352" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AF352" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AG352" t="s" s="2">
+        <v>1032</v>
+      </c>
+      <c r="AH352" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI352" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ352" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AK352" t="s" s="2">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="s" s="2">
+        <v>1001</v>
+      </c>
+      <c r="B353" t="s" s="2">
+        <v>1035</v>
+      </c>
+      <c r="C353" t="s" s="2">
+        <v>1035</v>
+      </c>
+      <c r="D353" s="2"/>
+      <c r="E353" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="F353" s="2"/>
+      <c r="G353" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H353" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I353" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="J353" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="K353" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L353" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="M353" t="s" s="2">
+        <v>1036</v>
+      </c>
+      <c r="N353" t="s" s="2">
+        <v>1037</v>
+      </c>
+      <c r="O353" s="2"/>
+      <c r="P353" s="2"/>
+      <c r="Q353" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="R353" s="2"/>
+      <c r="S353" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="T353" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="U353" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="V353" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="W353" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="X353" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Y353" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Z353" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AA353" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AB353" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AC353" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AD353" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AE353" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AF353" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AG353" t="s" s="2">
+        <v>1035</v>
+      </c>
+      <c r="AH353" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI353" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ353" t="s" s="2">
+        <v>1038</v>
+      </c>
+      <c r="AK353" t="s" s="2">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="s" s="2">
+        <v>1001</v>
+      </c>
+      <c r="B354" t="s" s="2">
+        <v>1039</v>
+      </c>
+      <c r="C354" t="s" s="2">
+        <v>1039</v>
+      </c>
+      <c r="D354" s="2"/>
+      <c r="E354" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="F354" s="2"/>
+      <c r="G354" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H354" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I354" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="J354" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="K354" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L354" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="M354" t="s" s="2">
+        <v>1040</v>
+      </c>
+      <c r="N354" t="s" s="2">
+        <v>1041</v>
+      </c>
+      <c r="O354" t="s" s="2">
+        <v>1042</v>
+      </c>
+      <c r="P354" s="2"/>
+      <c r="Q354" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="R354" s="2"/>
+      <c r="S354" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="T354" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="U354" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="V354" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="W354" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="X354" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Y354" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Z354" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AA354" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AB354" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AC354" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AD354" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AE354" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AF354" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AG354" t="s" s="2">
+        <v>1039</v>
+      </c>
+      <c r="AH354" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI354" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ354" t="s" s="2">
+        <v>1038</v>
+      </c>
+      <c r="AK354" t="s" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="s" s="2">
+        <v>1001</v>
+      </c>
+      <c r="B355" t="s" s="2">
+        <v>1043</v>
+      </c>
+      <c r="C355" t="s" s="2">
+        <v>1043</v>
+      </c>
+      <c r="D355" s="2"/>
+      <c r="E355" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="F355" s="2"/>
+      <c r="G355" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H355" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I355" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="J355" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="K355" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L355" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="M355" t="s" s="2">
+        <v>1044</v>
+      </c>
+      <c r="N355" t="s" s="2">
+        <v>1045</v>
+      </c>
+      <c r="O355" t="s" s="2">
+        <v>1046</v>
+      </c>
+      <c r="P355" s="2"/>
+      <c r="Q355" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="R355" s="2"/>
+      <c r="S355" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="T355" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="U355" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="V355" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="W355" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="X355" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Y355" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Z355" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AA355" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AB355" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AC355" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AD355" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AE355" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AF355" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AG355" t="s" s="2">
+        <v>1043</v>
+      </c>
+      <c r="AH355" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI355" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ355" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AK355" t="s" s="2">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="s" s="2">
+        <v>1001</v>
+      </c>
+      <c r="B356" t="s" s="2">
+        <v>1047</v>
+      </c>
+      <c r="C356" t="s" s="2">
+        <v>1022</v>
+      </c>
+      <c r="D356" t="s" s="2">
+        <v>1048</v>
+      </c>
+      <c r="E356" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="F356" s="2"/>
+      <c r="G356" t="s" s="2">
+        <v>1049</v>
+      </c>
+      <c r="H356" t="s" s="2">
+        <v>1049</v>
+      </c>
+      <c r="I356" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="J356" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="K356" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L356" t="s" s="2">
+        <v>722</v>
+      </c>
+      <c r="M356" t="s" s="2">
+        <v>1024</v>
+      </c>
+      <c r="N356" t="s" s="2">
+        <v>1025</v>
+      </c>
+      <c r="O356" s="2"/>
+      <c r="P356" s="2"/>
+      <c r="Q356" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="R356" s="2"/>
+      <c r="S356" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="T356" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="U356" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="V356" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="W356" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="X356" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Y356" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Z356" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AA356" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AB356" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AC356" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AD356" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AE356" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AF356" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AG356" t="s" s="2">
+        <v>1022</v>
+      </c>
+      <c r="AH356" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI356" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ356" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AK356" t="s" s="2">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="s" s="2">
+        <v>1001</v>
+      </c>
+      <c r="B357" t="s" s="2">
+        <v>1050</v>
+      </c>
+      <c r="C357" t="s" s="2">
+        <v>1029</v>
+      </c>
+      <c r="D357" s="2"/>
+      <c r="E357" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="F357" s="2"/>
+      <c r="G357" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H357" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I357" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="J357" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="K357" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="L357" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="M357" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="N357" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="O357" s="2"/>
+      <c r="P357" s="2"/>
+      <c r="Q357" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="R357" s="2"/>
+      <c r="S357" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="T357" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="U357" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="V357" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="W357" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="X357" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Y357" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Z357" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AA357" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AB357" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AC357" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AD357" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AE357" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AF357" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AG357" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AH357" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI357" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ357" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AK357" t="s" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="s" s="2">
+        <v>1001</v>
+      </c>
+      <c r="B358" t="s" s="2">
+        <v>1051</v>
+      </c>
+      <c r="C358" t="s" s="2">
+        <v>1030</v>
+      </c>
+      <c r="D358" s="2"/>
+      <c r="E358" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="F358" s="2"/>
+      <c r="G358" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H358" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I358" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="J358" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="K358" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="L358" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="M358" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="N358" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="O358" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="P358" s="2"/>
+      <c r="Q358" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="R358" s="2"/>
+      <c r="S358" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="T358" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="U358" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="V358" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="W358" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="X358" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Y358" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Z358" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AA358" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AB358" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AC358" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AD358" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AE358" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AF358" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AG358" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AH358" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI358" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ358" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AK358" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="s" s="2">
+        <v>1001</v>
+      </c>
+      <c r="B359" t="s" s="2">
+        <v>1052</v>
+      </c>
+      <c r="C359" t="s" s="2">
+        <v>1031</v>
+      </c>
+      <c r="D359" s="2"/>
+      <c r="E359" t="s" s="2">
+        <v>731</v>
+      </c>
+      <c r="F359" s="2"/>
+      <c r="G359" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H359" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I359" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="J359" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="K359" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L359" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="M359" t="s" s="2">
+        <v>732</v>
+      </c>
+      <c r="N359" t="s" s="2">
+        <v>733</v>
+      </c>
+      <c r="O359" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="P359" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="Q359" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="R359" s="2"/>
+      <c r="S359" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="T359" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="U359" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="V359" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="W359" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="X359" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Y359" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Z359" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AA359" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AB359" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AC359" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AD359" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AE359" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AF359" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AG359" t="s" s="2">
+        <v>734</v>
+      </c>
+      <c r="AH359" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI359" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ359" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AK359" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="s" s="2">
+        <v>1001</v>
+      </c>
+      <c r="B360" t="s" s="2">
+        <v>1053</v>
+      </c>
+      <c r="C360" t="s" s="2">
+        <v>1032</v>
+      </c>
+      <c r="D360" s="2"/>
+      <c r="E360" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="F360" s="2"/>
+      <c r="G360" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H360" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I360" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="J360" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="K360" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L360" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="M360" t="s" s="2">
+        <v>1033</v>
+      </c>
+      <c r="N360" t="s" s="2">
+        <v>1034</v>
+      </c>
+      <c r="O360" s="2"/>
+      <c r="P360" s="2"/>
+      <c r="Q360" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="R360" s="2"/>
+      <c r="S360" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="T360" t="s" s="2">
+        <v>1048</v>
+      </c>
+      <c r="U360" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="V360" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="W360" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="X360" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Y360" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Z360" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AA360" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AB360" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AC360" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AD360" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AE360" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AF360" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AG360" t="s" s="2">
+        <v>1032</v>
+      </c>
+      <c r="AH360" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI360" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ360" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AK360" t="s" s="2">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="s" s="2">
+        <v>1001</v>
+      </c>
+      <c r="B361" t="s" s="2">
+        <v>1054</v>
+      </c>
+      <c r="C361" t="s" s="2">
+        <v>1035</v>
+      </c>
+      <c r="D361" s="2"/>
+      <c r="E361" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="F361" s="2"/>
+      <c r="G361" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H361" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I361" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="J361" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="K361" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L361" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="M361" t="s" s="2">
+        <v>1036</v>
+      </c>
+      <c r="N361" t="s" s="2">
+        <v>1037</v>
+      </c>
+      <c r="O361" s="2"/>
+      <c r="P361" s="2"/>
+      <c r="Q361" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="R361" s="2"/>
+      <c r="S361" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="T361" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="U361" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="V361" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="W361" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="X361" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Y361" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Z361" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AA361" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AB361" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AC361" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AD361" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AE361" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AF361" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AG361" t="s" s="2">
+        <v>1035</v>
+      </c>
+      <c r="AH361" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI361" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ361" t="s" s="2">
+        <v>1038</v>
+      </c>
+      <c r="AK361" t="s" s="2">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="s" s="2">
+        <v>1001</v>
+      </c>
+      <c r="B362" t="s" s="2">
+        <v>1055</v>
+      </c>
+      <c r="C362" t="s" s="2">
+        <v>1039</v>
+      </c>
+      <c r="D362" s="2"/>
+      <c r="E362" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="F362" s="2"/>
+      <c r="G362" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H362" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I362" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="J362" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="K362" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L362" t="s" s="2">
+        <v>1056</v>
+      </c>
+      <c r="M362" t="s" s="2">
+        <v>1040</v>
+      </c>
+      <c r="N362" t="s" s="2">
+        <v>1041</v>
+      </c>
+      <c r="O362" t="s" s="2">
+        <v>1042</v>
+      </c>
+      <c r="P362" s="2"/>
+      <c r="Q362" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="R362" s="2"/>
+      <c r="S362" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="T362" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="U362" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="V362" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="W362" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="X362" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Y362" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Z362" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AA362" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AB362" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AC362" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AD362" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AE362" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AF362" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AG362" t="s" s="2">
+        <v>1039</v>
+      </c>
+      <c r="AH362" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI362" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ362" t="s" s="2">
+        <v>1038</v>
+      </c>
+      <c r="AK362" t="s" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="s" s="2">
+        <v>1001</v>
+      </c>
+      <c r="B363" t="s" s="2">
+        <v>1057</v>
+      </c>
+      <c r="C363" t="s" s="2">
+        <v>1043</v>
+      </c>
+      <c r="D363" s="2"/>
+      <c r="E363" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="F363" s="2"/>
+      <c r="G363" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H363" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I363" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="J363" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="K363" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L363" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="M363" t="s" s="2">
+        <v>1044</v>
+      </c>
+      <c r="N363" t="s" s="2">
+        <v>1045</v>
+      </c>
+      <c r="O363" t="s" s="2">
+        <v>1046</v>
+      </c>
+      <c r="P363" s="2"/>
+      <c r="Q363" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="R363" s="2"/>
+      <c r="S363" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="T363" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="U363" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="V363" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="W363" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="X363" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Y363" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Z363" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AA363" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AB363" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AC363" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AD363" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AE363" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AF363" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AG363" t="s" s="2">
+        <v>1043</v>
+      </c>
+      <c r="AH363" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI363" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ363" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AK363" t="s" s="2">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="s" s="2">
+        <v>1001</v>
+      </c>
+      <c r="B364" t="s" s="2">
+        <v>1058</v>
+      </c>
+      <c r="C364" t="s" s="2">
+        <v>1022</v>
+      </c>
+      <c r="D364" t="s" s="2">
+        <v>1059</v>
+      </c>
+      <c r="E364" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="F364" s="2"/>
+      <c r="G364" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H364" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I364" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="J364" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="K364" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L364" t="s" s="2">
+        <v>722</v>
+      </c>
+      <c r="M364" t="s" s="2">
+        <v>1024</v>
+      </c>
+      <c r="N364" t="s" s="2">
+        <v>1025</v>
+      </c>
+      <c r="O364" s="2"/>
+      <c r="P364" s="2"/>
+      <c r="Q364" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="R364" s="2"/>
+      <c r="S364" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="T364" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="U364" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="V364" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="W364" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="X364" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Y364" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Z364" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AA364" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AB364" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AC364" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AD364" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AE364" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AF364" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AG364" t="s" s="2">
+        <v>1022</v>
+      </c>
+      <c r="AH364" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI364" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ364" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AK364" t="s" s="2">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="s" s="2">
+        <v>1001</v>
+      </c>
+      <c r="B365" t="s" s="2">
+        <v>1060</v>
+      </c>
+      <c r="C365" t="s" s="2">
+        <v>1029</v>
+      </c>
+      <c r="D365" s="2"/>
+      <c r="E365" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="F365" s="2"/>
+      <c r="G365" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H365" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I365" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="J365" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="K365" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="L365" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="M365" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="N365" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="O365" s="2"/>
+      <c r="P365" s="2"/>
+      <c r="Q365" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="R365" s="2"/>
+      <c r="S365" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="T365" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="U365" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="V365" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="W365" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="X365" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Y365" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Z365" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AA365" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AB365" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AC365" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AD365" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AE365" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AF365" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AG365" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AH365" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI365" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ365" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AK365" t="s" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="s" s="2">
+        <v>1001</v>
+      </c>
+      <c r="B366" t="s" s="2">
+        <v>1061</v>
+      </c>
+      <c r="C366" t="s" s="2">
+        <v>1030</v>
+      </c>
+      <c r="D366" s="2"/>
+      <c r="E366" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="F366" s="2"/>
+      <c r="G366" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H366" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I366" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="J366" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="K366" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="L366" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="M366" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="N366" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="O366" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="P366" s="2"/>
+      <c r="Q366" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="R366" s="2"/>
+      <c r="S366" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="T366" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="U366" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="V366" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="W366" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="X366" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Y366" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Z366" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AA366" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AB366" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AC366" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AD366" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AE366" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AF366" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AG366" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AH366" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI366" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ366" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AK366" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="s" s="2">
+        <v>1001</v>
+      </c>
+      <c r="B367" t="s" s="2">
+        <v>1062</v>
+      </c>
+      <c r="C367" t="s" s="2">
+        <v>1031</v>
+      </c>
+      <c r="D367" s="2"/>
+      <c r="E367" t="s" s="2">
+        <v>731</v>
+      </c>
+      <c r="F367" s="2"/>
+      <c r="G367" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H367" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I367" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="J367" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="K367" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L367" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="M367" t="s" s="2">
+        <v>732</v>
+      </c>
+      <c r="N367" t="s" s="2">
+        <v>733</v>
+      </c>
+      <c r="O367" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="P367" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="Q367" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="R367" s="2"/>
+      <c r="S367" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="T367" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="U367" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="V367" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="W367" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="X367" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Y367" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Z367" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AA367" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AB367" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AC367" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AD367" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AE367" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AF367" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AG367" t="s" s="2">
+        <v>734</v>
+      </c>
+      <c r="AH367" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI367" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ367" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AK367" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="s" s="2">
+        <v>1001</v>
+      </c>
+      <c r="B368" t="s" s="2">
+        <v>1063</v>
+      </c>
+      <c r="C368" t="s" s="2">
+        <v>1032</v>
+      </c>
+      <c r="D368" s="2"/>
+      <c r="E368" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="F368" s="2"/>
+      <c r="G368" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H368" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I368" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="J368" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="K368" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L368" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="M368" t="s" s="2">
+        <v>1033</v>
+      </c>
+      <c r="N368" t="s" s="2">
+        <v>1034</v>
+      </c>
+      <c r="O368" s="2"/>
+      <c r="P368" s="2"/>
+      <c r="Q368" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="R368" s="2"/>
+      <c r="S368" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="T368" t="s" s="2">
+        <v>1059</v>
+      </c>
+      <c r="U368" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="V368" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="W368" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="X368" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Y368" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Z368" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AA368" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AB368" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AC368" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AD368" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AE368" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AF368" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AG368" t="s" s="2">
+        <v>1032</v>
+      </c>
+      <c r="AH368" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI368" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ368" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AK368" t="s" s="2">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="s" s="2">
+        <v>1001</v>
+      </c>
+      <c r="B369" t="s" s="2">
+        <v>1064</v>
+      </c>
+      <c r="C369" t="s" s="2">
+        <v>1035</v>
+      </c>
+      <c r="D369" s="2"/>
+      <c r="E369" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="F369" s="2"/>
+      <c r="G369" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H369" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I369" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="J369" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="K369" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L369" t="s" s="2">
+        <v>1065</v>
+      </c>
+      <c r="M369" t="s" s="2">
+        <v>1036</v>
+      </c>
+      <c r="N369" t="s" s="2">
+        <v>1037</v>
+      </c>
+      <c r="O369" s="2"/>
+      <c r="P369" s="2"/>
+      <c r="Q369" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="R369" s="2"/>
+      <c r="S369" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="T369" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="U369" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="V369" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="W369" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="X369" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Y369" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Z369" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AA369" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AB369" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AC369" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AD369" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AE369" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AF369" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AG369" t="s" s="2">
+        <v>1035</v>
+      </c>
+      <c r="AH369" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI369" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ369" t="s" s="2">
+        <v>1038</v>
+      </c>
+      <c r="AK369" t="s" s="2">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="s" s="2">
+        <v>1001</v>
+      </c>
+      <c r="B370" t="s" s="2">
+        <v>1066</v>
+      </c>
+      <c r="C370" t="s" s="2">
+        <v>1039</v>
+      </c>
+      <c r="D370" s="2"/>
+      <c r="E370" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="F370" s="2"/>
+      <c r="G370" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H370" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I370" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="J370" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="K370" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L370" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="M370" t="s" s="2">
+        <v>1040</v>
+      </c>
+      <c r="N370" t="s" s="2">
+        <v>1041</v>
+      </c>
+      <c r="O370" t="s" s="2">
+        <v>1042</v>
+      </c>
+      <c r="P370" s="2"/>
+      <c r="Q370" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="R370" s="2"/>
+      <c r="S370" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="T370" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="U370" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="V370" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="W370" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="X370" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Y370" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Z370" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AA370" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AB370" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AC370" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AD370" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AE370" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AF370" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AG370" t="s" s="2">
+        <v>1039</v>
+      </c>
+      <c r="AH370" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI370" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ370" t="s" s="2">
+        <v>1038</v>
+      </c>
+      <c r="AK370" t="s" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="s" s="2">
+        <v>1001</v>
+      </c>
+      <c r="B371" t="s" s="2">
+        <v>1067</v>
+      </c>
+      <c r="C371" t="s" s="2">
+        <v>1043</v>
+      </c>
+      <c r="D371" s="2"/>
+      <c r="E371" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="F371" s="2"/>
+      <c r="G371" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H371" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I371" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="J371" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="K371" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L371" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="M371" t="s" s="2">
+        <v>1044</v>
+      </c>
+      <c r="N371" t="s" s="2">
+        <v>1045</v>
+      </c>
+      <c r="O371" t="s" s="2">
+        <v>1046</v>
+      </c>
+      <c r="P371" s="2"/>
+      <c r="Q371" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="R371" s="2"/>
+      <c r="S371" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="T371" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="U371" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="V371" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="W371" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="X371" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Y371" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Z371" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AA371" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AB371" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AC371" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AD371" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AE371" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AF371" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AG371" t="s" s="2">
+        <v>1043</v>
+      </c>
+      <c r="AH371" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI371" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ371" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AK371" t="s" s="2">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="s" s="2">
+        <v>1001</v>
+      </c>
+      <c r="B372" t="s" s="2">
+        <v>1068</v>
+      </c>
+      <c r="C372" t="s" s="2">
+        <v>1022</v>
+      </c>
+      <c r="D372" t="s" s="2">
+        <v>1069</v>
+      </c>
+      <c r="E372" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="F372" s="2"/>
+      <c r="G372" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H372" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I372" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="J372" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="K372" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L372" t="s" s="2">
+        <v>722</v>
+      </c>
+      <c r="M372" t="s" s="2">
+        <v>1024</v>
+      </c>
+      <c r="N372" t="s" s="2">
+        <v>1025</v>
+      </c>
+      <c r="O372" s="2"/>
+      <c r="P372" s="2"/>
+      <c r="Q372" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="R372" s="2"/>
+      <c r="S372" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="T372" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="U372" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="V372" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="W372" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="X372" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Y372" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Z372" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AA372" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AB372" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AC372" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AD372" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AE372" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AF372" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AG372" t="s" s="2">
+        <v>1022</v>
+      </c>
+      <c r="AH372" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI372" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ372" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AK372" t="s" s="2">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="s" s="2">
+        <v>1001</v>
+      </c>
+      <c r="B373" t="s" s="2">
+        <v>1070</v>
+      </c>
+      <c r="C373" t="s" s="2">
+        <v>1029</v>
+      </c>
+      <c r="D373" s="2"/>
+      <c r="E373" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="F373" s="2"/>
+      <c r="G373" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H373" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I373" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="J373" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="K373" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="L373" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="M373" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="N373" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="O373" s="2"/>
+      <c r="P373" s="2"/>
+      <c r="Q373" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="R373" s="2"/>
+      <c r="S373" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="T373" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="U373" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="V373" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="W373" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="X373" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Y373" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Z373" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AA373" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AB373" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AC373" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AD373" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AE373" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AF373" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AG373" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AH373" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI373" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ373" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AK373" t="s" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="s" s="2">
+        <v>1001</v>
+      </c>
+      <c r="B374" t="s" s="2">
+        <v>1071</v>
+      </c>
+      <c r="C374" t="s" s="2">
+        <v>1030</v>
+      </c>
+      <c r="D374" s="2"/>
+      <c r="E374" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="F374" s="2"/>
+      <c r="G374" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H374" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I374" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="J374" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="K374" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="L374" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="M374" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="N374" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="O374" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="P374" s="2"/>
+      <c r="Q374" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="R374" s="2"/>
+      <c r="S374" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="T374" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="U374" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="V374" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="W374" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="X374" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Y374" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Z374" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AA374" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AB374" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AC374" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AD374" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AE374" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AF374" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AG374" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AH374" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI374" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ374" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AK374" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="s" s="2">
+        <v>1001</v>
+      </c>
+      <c r="B375" t="s" s="2">
+        <v>1072</v>
+      </c>
+      <c r="C375" t="s" s="2">
+        <v>1031</v>
+      </c>
+      <c r="D375" s="2"/>
+      <c r="E375" t="s" s="2">
+        <v>731</v>
+      </c>
+      <c r="F375" s="2"/>
+      <c r="G375" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H375" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I375" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="J375" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="K375" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L375" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="M375" t="s" s="2">
+        <v>732</v>
+      </c>
+      <c r="N375" t="s" s="2">
+        <v>733</v>
+      </c>
+      <c r="O375" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="P375" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="Q375" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="R375" s="2"/>
+      <c r="S375" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="T375" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="U375" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="V375" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="W375" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="X375" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Y375" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Z375" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AA375" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AB375" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AC375" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AD375" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AE375" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AF375" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AG375" t="s" s="2">
+        <v>734</v>
+      </c>
+      <c r="AH375" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI375" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ375" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AK375" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="s" s="2">
+        <v>1001</v>
+      </c>
+      <c r="B376" t="s" s="2">
+        <v>1073</v>
+      </c>
+      <c r="C376" t="s" s="2">
+        <v>1032</v>
+      </c>
+      <c r="D376" s="2"/>
+      <c r="E376" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="F376" s="2"/>
+      <c r="G376" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H376" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I376" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="J376" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="K376" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L376" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="M376" t="s" s="2">
+        <v>1033</v>
+      </c>
+      <c r="N376" t="s" s="2">
+        <v>1034</v>
+      </c>
+      <c r="O376" s="2"/>
+      <c r="P376" s="2"/>
+      <c r="Q376" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="R376" s="2"/>
+      <c r="S376" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="T376" t="s" s="2">
+        <v>1069</v>
+      </c>
+      <c r="U376" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="V376" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="W376" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="X376" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Y376" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Z376" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AA376" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AB376" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AC376" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AD376" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AE376" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AF376" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AG376" t="s" s="2">
+        <v>1032</v>
+      </c>
+      <c r="AH376" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI376" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ376" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AK376" t="s" s="2">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="s" s="2">
+        <v>1001</v>
+      </c>
+      <c r="B377" t="s" s="2">
+        <v>1074</v>
+      </c>
+      <c r="C377" t="s" s="2">
+        <v>1035</v>
+      </c>
+      <c r="D377" s="2"/>
+      <c r="E377" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="F377" s="2"/>
+      <c r="G377" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H377" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I377" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="J377" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="K377" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L377" t="s" s="2">
+        <v>1065</v>
+      </c>
+      <c r="M377" t="s" s="2">
+        <v>1036</v>
+      </c>
+      <c r="N377" t="s" s="2">
+        <v>1037</v>
+      </c>
+      <c r="O377" s="2"/>
+      <c r="P377" s="2"/>
+      <c r="Q377" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="R377" s="2"/>
+      <c r="S377" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="T377" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="U377" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="V377" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="W377" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="X377" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Y377" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Z377" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AA377" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AB377" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AC377" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AD377" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AE377" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AF377" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AG377" t="s" s="2">
+        <v>1035</v>
+      </c>
+      <c r="AH377" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI377" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ377" t="s" s="2">
+        <v>1038</v>
+      </c>
+      <c r="AK377" t="s" s="2">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="s" s="2">
+        <v>1001</v>
+      </c>
+      <c r="B378" t="s" s="2">
+        <v>1075</v>
+      </c>
+      <c r="C378" t="s" s="2">
+        <v>1039</v>
+      </c>
+      <c r="D378" s="2"/>
+      <c r="E378" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="F378" s="2"/>
+      <c r="G378" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H378" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I378" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="J378" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="K378" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L378" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="M378" t="s" s="2">
+        <v>1040</v>
+      </c>
+      <c r="N378" t="s" s="2">
+        <v>1041</v>
+      </c>
+      <c r="O378" t="s" s="2">
+        <v>1042</v>
+      </c>
+      <c r="P378" s="2"/>
+      <c r="Q378" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="R378" s="2"/>
+      <c r="S378" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="T378" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="U378" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="V378" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="W378" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="X378" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Y378" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Z378" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AA378" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AB378" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AC378" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AD378" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AE378" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AF378" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AG378" t="s" s="2">
+        <v>1039</v>
+      </c>
+      <c r="AH378" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI378" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ378" t="s" s="2">
+        <v>1038</v>
+      </c>
+      <c r="AK378" t="s" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="s" s="2">
+        <v>1001</v>
+      </c>
+      <c r="B379" t="s" s="2">
+        <v>1076</v>
+      </c>
+      <c r="C379" t="s" s="2">
+        <v>1043</v>
+      </c>
+      <c r="D379" s="2"/>
+      <c r="E379" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="F379" s="2"/>
+      <c r="G379" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H379" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I379" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="J379" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="K379" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L379" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="M379" t="s" s="2">
+        <v>1044</v>
+      </c>
+      <c r="N379" t="s" s="2">
+        <v>1045</v>
+      </c>
+      <c r="O379" t="s" s="2">
+        <v>1046</v>
+      </c>
+      <c r="P379" s="2"/>
+      <c r="Q379" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="R379" s="2"/>
+      <c r="S379" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="T379" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="U379" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="V379" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="W379" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="X379" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Y379" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Z379" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AA379" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AB379" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AC379" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AD379" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AE379" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AF379" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AG379" t="s" s="2">
+        <v>1043</v>
+      </c>
+      <c r="AH379" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI379" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ379" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AK379" t="s" s="2">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="s" s="2">
+        <v>1001</v>
+      </c>
+      <c r="B380" t="s" s="2">
+        <v>1077</v>
+      </c>
+      <c r="C380" t="s" s="2">
+        <v>1022</v>
+      </c>
+      <c r="D380" t="s" s="2">
+        <v>1078</v>
+      </c>
+      <c r="E380" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="F380" s="2"/>
+      <c r="G380" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H380" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I380" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="J380" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="K380" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L380" t="s" s="2">
+        <v>722</v>
+      </c>
+      <c r="M380" t="s" s="2">
+        <v>1024</v>
+      </c>
+      <c r="N380" t="s" s="2">
+        <v>1025</v>
+      </c>
+      <c r="O380" s="2"/>
+      <c r="P380" s="2"/>
+      <c r="Q380" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="R380" s="2"/>
+      <c r="S380" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="T380" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="U380" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="V380" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="W380" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="X380" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Y380" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Z380" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AA380" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AB380" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AC380" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AD380" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AE380" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AF380" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AG380" t="s" s="2">
+        <v>1022</v>
+      </c>
+      <c r="AH380" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI380" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ380" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AK380" t="s" s="2">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="s" s="2">
+        <v>1001</v>
+      </c>
+      <c r="B381" t="s" s="2">
+        <v>1079</v>
+      </c>
+      <c r="C381" t="s" s="2">
+        <v>1029</v>
+      </c>
+      <c r="D381" s="2"/>
+      <c r="E381" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="F381" s="2"/>
+      <c r="G381" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H381" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I381" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="J381" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="K381" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="L381" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="M381" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="N381" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="O381" s="2"/>
+      <c r="P381" s="2"/>
+      <c r="Q381" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="R381" s="2"/>
+      <c r="S381" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="T381" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="U381" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="V381" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="W381" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="X381" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Y381" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Z381" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AA381" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AB381" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AC381" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AD381" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AE381" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AF381" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AG381" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AH381" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI381" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ381" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AK381" t="s" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="s" s="2">
+        <v>1001</v>
+      </c>
+      <c r="B382" t="s" s="2">
+        <v>1080</v>
+      </c>
+      <c r="C382" t="s" s="2">
+        <v>1030</v>
+      </c>
+      <c r="D382" s="2"/>
+      <c r="E382" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="F382" s="2"/>
+      <c r="G382" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H382" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I382" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="J382" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="K382" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="L382" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="M382" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="N382" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="O382" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="P382" s="2"/>
+      <c r="Q382" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="R382" s="2"/>
+      <c r="S382" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="T382" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="U382" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="V382" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="W382" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="X382" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Y382" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Z382" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AA382" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AB382" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AC382" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AD382" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AE382" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AF382" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AG382" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AH382" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI382" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ382" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AK382" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="s" s="2">
+        <v>1001</v>
+      </c>
+      <c r="B383" t="s" s="2">
+        <v>1081</v>
+      </c>
+      <c r="C383" t="s" s="2">
+        <v>1031</v>
+      </c>
+      <c r="D383" s="2"/>
+      <c r="E383" t="s" s="2">
+        <v>731</v>
+      </c>
+      <c r="F383" s="2"/>
+      <c r="G383" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H383" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I383" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="J383" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="K383" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L383" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="M383" t="s" s="2">
+        <v>732</v>
+      </c>
+      <c r="N383" t="s" s="2">
+        <v>733</v>
+      </c>
+      <c r="O383" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="P383" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="Q383" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="R383" s="2"/>
+      <c r="S383" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="T383" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="U383" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="V383" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="W383" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="X383" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Y383" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Z383" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AA383" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AB383" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AC383" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AD383" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AE383" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AF383" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AG383" t="s" s="2">
+        <v>734</v>
+      </c>
+      <c r="AH383" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI383" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ383" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AK383" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="s" s="2">
+        <v>1001</v>
+      </c>
+      <c r="B384" t="s" s="2">
+        <v>1082</v>
+      </c>
+      <c r="C384" t="s" s="2">
+        <v>1032</v>
+      </c>
+      <c r="D384" s="2"/>
+      <c r="E384" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="F384" s="2"/>
+      <c r="G384" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H384" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I384" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="J384" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="K384" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L384" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="M384" t="s" s="2">
+        <v>1033</v>
+      </c>
+      <c r="N384" t="s" s="2">
+        <v>1034</v>
+      </c>
+      <c r="O384" s="2"/>
+      <c r="P384" s="2"/>
+      <c r="Q384" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="R384" s="2"/>
+      <c r="S384" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="T384" t="s" s="2">
+        <v>1078</v>
+      </c>
+      <c r="U384" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="V384" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="W384" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="X384" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Y384" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Z384" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AA384" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AB384" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AC384" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AD384" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AE384" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AF384" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AG384" t="s" s="2">
+        <v>1032</v>
+      </c>
+      <c r="AH384" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI384" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ384" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AK384" t="s" s="2">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="s" s="2">
+        <v>1001</v>
+      </c>
+      <c r="B385" t="s" s="2">
+        <v>1083</v>
+      </c>
+      <c r="C385" t="s" s="2">
+        <v>1035</v>
+      </c>
+      <c r="D385" s="2"/>
+      <c r="E385" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="F385" s="2"/>
+      <c r="G385" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H385" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I385" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="J385" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="K385" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L385" t="s" s="2">
+        <v>1084</v>
+      </c>
+      <c r="M385" t="s" s="2">
+        <v>1036</v>
+      </c>
+      <c r="N385" t="s" s="2">
+        <v>1037</v>
+      </c>
+      <c r="O385" s="2"/>
+      <c r="P385" s="2"/>
+      <c r="Q385" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="R385" s="2"/>
+      <c r="S385" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="T385" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="U385" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="V385" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="W385" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="X385" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Y385" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Z385" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AA385" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AB385" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AC385" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AD385" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AE385" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AF385" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AG385" t="s" s="2">
+        <v>1035</v>
+      </c>
+      <c r="AH385" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI385" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ385" t="s" s="2">
+        <v>1038</v>
+      </c>
+      <c r="AK385" t="s" s="2">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="s" s="2">
+        <v>1001</v>
+      </c>
+      <c r="B386" t="s" s="2">
+        <v>1085</v>
+      </c>
+      <c r="C386" t="s" s="2">
+        <v>1039</v>
+      </c>
+      <c r="D386" s="2"/>
+      <c r="E386" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="F386" s="2"/>
+      <c r="G386" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H386" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I386" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="J386" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="K386" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L386" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="M386" t="s" s="2">
+        <v>1040</v>
+      </c>
+      <c r="N386" t="s" s="2">
+        <v>1041</v>
+      </c>
+      <c r="O386" t="s" s="2">
+        <v>1042</v>
+      </c>
+      <c r="P386" s="2"/>
+      <c r="Q386" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="R386" s="2"/>
+      <c r="S386" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="T386" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="U386" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="V386" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="W386" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="X386" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Y386" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Z386" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AA386" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AB386" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AC386" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AD386" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AE386" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AF386" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AG386" t="s" s="2">
+        <v>1039</v>
+      </c>
+      <c r="AH386" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI386" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ386" t="s" s="2">
+        <v>1038</v>
+      </c>
+      <c r="AK386" t="s" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="s" s="2">
+        <v>1001</v>
+      </c>
+      <c r="B387" t="s" s="2">
+        <v>1086</v>
+      </c>
+      <c r="C387" t="s" s="2">
+        <v>1043</v>
+      </c>
+      <c r="D387" s="2"/>
+      <c r="E387" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="F387" s="2"/>
+      <c r="G387" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H387" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I387" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="J387" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="K387" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L387" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="M387" t="s" s="2">
+        <v>1044</v>
+      </c>
+      <c r="N387" t="s" s="2">
+        <v>1045</v>
+      </c>
+      <c r="O387" t="s" s="2">
+        <v>1046</v>
+      </c>
+      <c r="P387" s="2"/>
+      <c r="Q387" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="R387" s="2"/>
+      <c r="S387" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="T387" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="U387" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="V387" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="W387" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="X387" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Y387" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Z387" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AA387" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AB387" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AC387" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AD387" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AE387" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AF387" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AG387" t="s" s="2">
+        <v>1043</v>
+      </c>
+      <c r="AH387" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI387" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ387" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AK387" t="s" s="2">
+        <v>121</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/main/all-profiles.xlsx
+++ b/main/all-profiles.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12922" uniqueCount="1087">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13706" uniqueCount="1117">
   <si>
     <t>Property</t>
   </si>
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2026.1.0</t>
+    <t>2026.2.0-rc</t>
   </si>
   <si>
     <t>Name</t>
@@ -3176,7 +3176,7 @@
     <t>Parameters.parameter</t>
   </si>
   <si>
-    <t>5</t>
+    <t>8</t>
   </si>
   <si>
     <t>Operation Parameter</t>
@@ -3341,6 +3341,97 @@
   </si>
   <si>
     <t>Parameters.parameter:matchResult.part</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:matchCreated</t>
+  </si>
+  <si>
+    <t>matchCreated</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:matchCreated.id</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:matchCreated.extension</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:matchCreated.modifierExtension</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:matchCreated.name</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:matchCreated.value[x]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dateTime
+</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:matchCreated.resource</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:matchCreated.part</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:matchCreationType</t>
+  </si>
+  <si>
+    <t>matchCreationType</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:matchCreationType.id</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:matchCreationType.extension</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:matchCreationType.modifierExtension</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:matchCreationType.name</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:matchCreationType.value[x]</t>
+  </si>
+  <si>
+    <t>https://ths-greifswald.de/fhir/epix/ValueSet/MatchCreationTypeVS</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:matchCreationType.resource</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:matchCreationType.part</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:matchPriority</t>
+  </si>
+  <si>
+    <t>matchPriority</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:matchPriority.id</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:matchPriority.extension</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:matchPriority.modifierExtension</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:matchPriority.name</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:matchPriority.value[x]</t>
+  </si>
+  <si>
+    <t>https://ths-greifswald.de/fhir/epix/ValueSet/MatchPriorityVS</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:matchPriority.resource</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:matchPriority.part</t>
   </si>
   <si>
     <t>Parameters.parameter:linkId</t>
@@ -4199,13 +4290,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK387"/>
+  <dimension ref="A1:AK411"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="21.1171875" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="59.46484375" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="46.26171875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="14.98046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="16.40625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="34.21875" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="14.98046875" customWidth="true" bestFit="true"/>
     <col min="7" max="7" width="4.23828125" customWidth="true" bestFit="true"/>
@@ -4221,14 +4312,14 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="10.79296875" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="16.40625" customWidth="true" bestFit="true"/>
     <col min="21" max="21" width="34.26953125" customWidth="true" bestFit="true"/>
     <col min="22" max="22" width="14.72265625" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="15.13671875" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="87.8671875" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="48.33203125" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="52.60546875" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="36.0390625" customWidth="true" bestFit="true"/>
@@ -44770,6 +44861,2510 @@
         <v>121</v>
       </c>
     </row>
+    <row r="388">
+      <c r="A388" t="s" s="2">
+        <v>1001</v>
+      </c>
+      <c r="B388" t="s" s="2">
+        <v>1087</v>
+      </c>
+      <c r="C388" t="s" s="2">
+        <v>1022</v>
+      </c>
+      <c r="D388" t="s" s="2">
+        <v>1088</v>
+      </c>
+      <c r="E388" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="F388" s="2"/>
+      <c r="G388" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H388" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I388" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="J388" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="K388" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L388" t="s" s="2">
+        <v>722</v>
+      </c>
+      <c r="M388" t="s" s="2">
+        <v>1024</v>
+      </c>
+      <c r="N388" t="s" s="2">
+        <v>1025</v>
+      </c>
+      <c r="O388" s="2"/>
+      <c r="P388" s="2"/>
+      <c r="Q388" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="R388" s="2"/>
+      <c r="S388" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="T388" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="U388" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="V388" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="W388" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="X388" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Y388" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Z388" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AA388" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AB388" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AC388" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AD388" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AE388" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AF388" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AG388" t="s" s="2">
+        <v>1022</v>
+      </c>
+      <c r="AH388" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI388" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ388" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AK388" t="s" s="2">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="s" s="2">
+        <v>1001</v>
+      </c>
+      <c r="B389" t="s" s="2">
+        <v>1089</v>
+      </c>
+      <c r="C389" t="s" s="2">
+        <v>1029</v>
+      </c>
+      <c r="D389" s="2"/>
+      <c r="E389" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="F389" s="2"/>
+      <c r="G389" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H389" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I389" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="J389" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="K389" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="L389" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="M389" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="N389" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="O389" s="2"/>
+      <c r="P389" s="2"/>
+      <c r="Q389" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="R389" s="2"/>
+      <c r="S389" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="T389" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="U389" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="V389" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="W389" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="X389" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Y389" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Z389" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AA389" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AB389" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AC389" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AD389" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AE389" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AF389" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AG389" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AH389" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI389" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ389" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AK389" t="s" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="s" s="2">
+        <v>1001</v>
+      </c>
+      <c r="B390" t="s" s="2">
+        <v>1090</v>
+      </c>
+      <c r="C390" t="s" s="2">
+        <v>1030</v>
+      </c>
+      <c r="D390" s="2"/>
+      <c r="E390" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="F390" s="2"/>
+      <c r="G390" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H390" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I390" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="J390" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="K390" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="L390" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="M390" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="N390" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="O390" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="P390" s="2"/>
+      <c r="Q390" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="R390" s="2"/>
+      <c r="S390" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="T390" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="U390" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="V390" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="W390" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="X390" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Y390" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Z390" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AA390" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AB390" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AC390" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AD390" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AE390" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AF390" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AG390" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AH390" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI390" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ390" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AK390" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="s" s="2">
+        <v>1001</v>
+      </c>
+      <c r="B391" t="s" s="2">
+        <v>1091</v>
+      </c>
+      <c r="C391" t="s" s="2">
+        <v>1031</v>
+      </c>
+      <c r="D391" s="2"/>
+      <c r="E391" t="s" s="2">
+        <v>731</v>
+      </c>
+      <c r="F391" s="2"/>
+      <c r="G391" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H391" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I391" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="J391" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="K391" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L391" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="M391" t="s" s="2">
+        <v>732</v>
+      </c>
+      <c r="N391" t="s" s="2">
+        <v>733</v>
+      </c>
+      <c r="O391" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="P391" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="Q391" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="R391" s="2"/>
+      <c r="S391" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="T391" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="U391" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="V391" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="W391" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="X391" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Y391" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Z391" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AA391" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AB391" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AC391" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AD391" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AE391" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AF391" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AG391" t="s" s="2">
+        <v>734</v>
+      </c>
+      <c r="AH391" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI391" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ391" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AK391" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="s" s="2">
+        <v>1001</v>
+      </c>
+      <c r="B392" t="s" s="2">
+        <v>1092</v>
+      </c>
+      <c r="C392" t="s" s="2">
+        <v>1032</v>
+      </c>
+      <c r="D392" s="2"/>
+      <c r="E392" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="F392" s="2"/>
+      <c r="G392" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H392" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I392" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="J392" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="K392" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L392" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="M392" t="s" s="2">
+        <v>1033</v>
+      </c>
+      <c r="N392" t="s" s="2">
+        <v>1034</v>
+      </c>
+      <c r="O392" s="2"/>
+      <c r="P392" s="2"/>
+      <c r="Q392" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="R392" s="2"/>
+      <c r="S392" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="T392" t="s" s="2">
+        <v>1088</v>
+      </c>
+      <c r="U392" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="V392" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="W392" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="X392" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Y392" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Z392" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AA392" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AB392" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AC392" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AD392" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AE392" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AF392" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AG392" t="s" s="2">
+        <v>1032</v>
+      </c>
+      <c r="AH392" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI392" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ392" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AK392" t="s" s="2">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="s" s="2">
+        <v>1001</v>
+      </c>
+      <c r="B393" t="s" s="2">
+        <v>1093</v>
+      </c>
+      <c r="C393" t="s" s="2">
+        <v>1035</v>
+      </c>
+      <c r="D393" s="2"/>
+      <c r="E393" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="F393" s="2"/>
+      <c r="G393" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H393" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I393" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="J393" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="K393" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L393" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="M393" t="s" s="2">
+        <v>1036</v>
+      </c>
+      <c r="N393" t="s" s="2">
+        <v>1037</v>
+      </c>
+      <c r="O393" s="2"/>
+      <c r="P393" s="2"/>
+      <c r="Q393" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="R393" s="2"/>
+      <c r="S393" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="T393" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="U393" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="V393" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="W393" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="X393" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Y393" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="Z393" s="2"/>
+      <c r="AA393" t="s" s="2">
+        <v>1094</v>
+      </c>
+      <c r="AB393" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AC393" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AD393" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AE393" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AF393" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AG393" t="s" s="2">
+        <v>1035</v>
+      </c>
+      <c r="AH393" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI393" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ393" t="s" s="2">
+        <v>1038</v>
+      </c>
+      <c r="AK393" t="s" s="2">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="s" s="2">
+        <v>1001</v>
+      </c>
+      <c r="B394" t="s" s="2">
+        <v>1095</v>
+      </c>
+      <c r="C394" t="s" s="2">
+        <v>1039</v>
+      </c>
+      <c r="D394" s="2"/>
+      <c r="E394" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="F394" s="2"/>
+      <c r="G394" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H394" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I394" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="J394" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="K394" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L394" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="M394" t="s" s="2">
+        <v>1040</v>
+      </c>
+      <c r="N394" t="s" s="2">
+        <v>1041</v>
+      </c>
+      <c r="O394" t="s" s="2">
+        <v>1042</v>
+      </c>
+      <c r="P394" s="2"/>
+      <c r="Q394" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="R394" s="2"/>
+      <c r="S394" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="T394" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="U394" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="V394" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="W394" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="X394" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Y394" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Z394" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AA394" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AB394" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AC394" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AD394" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AE394" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AF394" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AG394" t="s" s="2">
+        <v>1039</v>
+      </c>
+      <c r="AH394" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI394" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ394" t="s" s="2">
+        <v>1038</v>
+      </c>
+      <c r="AK394" t="s" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="s" s="2">
+        <v>1001</v>
+      </c>
+      <c r="B395" t="s" s="2">
+        <v>1096</v>
+      </c>
+      <c r="C395" t="s" s="2">
+        <v>1043</v>
+      </c>
+      <c r="D395" s="2"/>
+      <c r="E395" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="F395" s="2"/>
+      <c r="G395" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H395" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I395" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="J395" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="K395" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L395" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="M395" t="s" s="2">
+        <v>1044</v>
+      </c>
+      <c r="N395" t="s" s="2">
+        <v>1045</v>
+      </c>
+      <c r="O395" t="s" s="2">
+        <v>1046</v>
+      </c>
+      <c r="P395" s="2"/>
+      <c r="Q395" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="R395" s="2"/>
+      <c r="S395" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="T395" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="U395" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="V395" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="W395" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="X395" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Y395" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Z395" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AA395" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AB395" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AC395" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AD395" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AE395" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AF395" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AG395" t="s" s="2">
+        <v>1043</v>
+      </c>
+      <c r="AH395" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI395" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ395" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AK395" t="s" s="2">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="s" s="2">
+        <v>1001</v>
+      </c>
+      <c r="B396" t="s" s="2">
+        <v>1097</v>
+      </c>
+      <c r="C396" t="s" s="2">
+        <v>1022</v>
+      </c>
+      <c r="D396" t="s" s="2">
+        <v>1098</v>
+      </c>
+      <c r="E396" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="F396" s="2"/>
+      <c r="G396" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H396" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I396" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="J396" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="K396" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L396" t="s" s="2">
+        <v>722</v>
+      </c>
+      <c r="M396" t="s" s="2">
+        <v>1024</v>
+      </c>
+      <c r="N396" t="s" s="2">
+        <v>1025</v>
+      </c>
+      <c r="O396" s="2"/>
+      <c r="P396" s="2"/>
+      <c r="Q396" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="R396" s="2"/>
+      <c r="S396" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="T396" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="U396" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="V396" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="W396" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="X396" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Y396" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Z396" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AA396" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AB396" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AC396" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AD396" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AE396" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AF396" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AG396" t="s" s="2">
+        <v>1022</v>
+      </c>
+      <c r="AH396" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI396" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ396" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AK396" t="s" s="2">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="s" s="2">
+        <v>1001</v>
+      </c>
+      <c r="B397" t="s" s="2">
+        <v>1099</v>
+      </c>
+      <c r="C397" t="s" s="2">
+        <v>1029</v>
+      </c>
+      <c r="D397" s="2"/>
+      <c r="E397" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="F397" s="2"/>
+      <c r="G397" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H397" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I397" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="J397" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="K397" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="L397" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="M397" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="N397" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="O397" s="2"/>
+      <c r="P397" s="2"/>
+      <c r="Q397" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="R397" s="2"/>
+      <c r="S397" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="T397" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="U397" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="V397" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="W397" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="X397" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Y397" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Z397" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AA397" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AB397" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AC397" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AD397" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AE397" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AF397" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AG397" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AH397" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI397" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ397" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AK397" t="s" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="s" s="2">
+        <v>1001</v>
+      </c>
+      <c r="B398" t="s" s="2">
+        <v>1100</v>
+      </c>
+      <c r="C398" t="s" s="2">
+        <v>1030</v>
+      </c>
+      <c r="D398" s="2"/>
+      <c r="E398" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="F398" s="2"/>
+      <c r="G398" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H398" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I398" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="J398" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="K398" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="L398" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="M398" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="N398" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="O398" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="P398" s="2"/>
+      <c r="Q398" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="R398" s="2"/>
+      <c r="S398" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="T398" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="U398" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="V398" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="W398" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="X398" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Y398" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Z398" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AA398" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AB398" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AC398" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AD398" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AE398" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AF398" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AG398" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AH398" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI398" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ398" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AK398" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="s" s="2">
+        <v>1001</v>
+      </c>
+      <c r="B399" t="s" s="2">
+        <v>1101</v>
+      </c>
+      <c r="C399" t="s" s="2">
+        <v>1031</v>
+      </c>
+      <c r="D399" s="2"/>
+      <c r="E399" t="s" s="2">
+        <v>731</v>
+      </c>
+      <c r="F399" s="2"/>
+      <c r="G399" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H399" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I399" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="J399" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="K399" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L399" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="M399" t="s" s="2">
+        <v>732</v>
+      </c>
+      <c r="N399" t="s" s="2">
+        <v>733</v>
+      </c>
+      <c r="O399" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="P399" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="Q399" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="R399" s="2"/>
+      <c r="S399" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="T399" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="U399" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="V399" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="W399" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="X399" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Y399" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Z399" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AA399" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AB399" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AC399" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AD399" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AE399" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AF399" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AG399" t="s" s="2">
+        <v>734</v>
+      </c>
+      <c r="AH399" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI399" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ399" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AK399" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="s" s="2">
+        <v>1001</v>
+      </c>
+      <c r="B400" t="s" s="2">
+        <v>1102</v>
+      </c>
+      <c r="C400" t="s" s="2">
+        <v>1032</v>
+      </c>
+      <c r="D400" s="2"/>
+      <c r="E400" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="F400" s="2"/>
+      <c r="G400" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H400" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I400" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="J400" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="K400" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L400" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="M400" t="s" s="2">
+        <v>1033</v>
+      </c>
+      <c r="N400" t="s" s="2">
+        <v>1034</v>
+      </c>
+      <c r="O400" s="2"/>
+      <c r="P400" s="2"/>
+      <c r="Q400" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="R400" s="2"/>
+      <c r="S400" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="T400" t="s" s="2">
+        <v>1098</v>
+      </c>
+      <c r="U400" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="V400" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="W400" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="X400" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Y400" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Z400" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AA400" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AB400" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AC400" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AD400" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AE400" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AF400" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AG400" t="s" s="2">
+        <v>1032</v>
+      </c>
+      <c r="AH400" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI400" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ400" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AK400" t="s" s="2">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="s" s="2">
+        <v>1001</v>
+      </c>
+      <c r="B401" t="s" s="2">
+        <v>1103</v>
+      </c>
+      <c r="C401" t="s" s="2">
+        <v>1035</v>
+      </c>
+      <c r="D401" s="2"/>
+      <c r="E401" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="F401" s="2"/>
+      <c r="G401" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H401" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I401" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="J401" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="K401" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L401" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="M401" t="s" s="2">
+        <v>1036</v>
+      </c>
+      <c r="N401" t="s" s="2">
+        <v>1037</v>
+      </c>
+      <c r="O401" s="2"/>
+      <c r="P401" s="2"/>
+      <c r="Q401" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="R401" s="2"/>
+      <c r="S401" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="T401" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="U401" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="V401" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="W401" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="X401" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Y401" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="Z401" s="2"/>
+      <c r="AA401" t="s" s="2">
+        <v>1104</v>
+      </c>
+      <c r="AB401" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AC401" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AD401" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AE401" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AF401" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AG401" t="s" s="2">
+        <v>1035</v>
+      </c>
+      <c r="AH401" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI401" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ401" t="s" s="2">
+        <v>1038</v>
+      </c>
+      <c r="AK401" t="s" s="2">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="s" s="2">
+        <v>1001</v>
+      </c>
+      <c r="B402" t="s" s="2">
+        <v>1105</v>
+      </c>
+      <c r="C402" t="s" s="2">
+        <v>1039</v>
+      </c>
+      <c r="D402" s="2"/>
+      <c r="E402" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="F402" s="2"/>
+      <c r="G402" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H402" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I402" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="J402" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="K402" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L402" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="M402" t="s" s="2">
+        <v>1040</v>
+      </c>
+      <c r="N402" t="s" s="2">
+        <v>1041</v>
+      </c>
+      <c r="O402" t="s" s="2">
+        <v>1042</v>
+      </c>
+      <c r="P402" s="2"/>
+      <c r="Q402" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="R402" s="2"/>
+      <c r="S402" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="T402" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="U402" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="V402" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="W402" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="X402" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Y402" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Z402" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AA402" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AB402" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AC402" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AD402" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AE402" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AF402" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AG402" t="s" s="2">
+        <v>1039</v>
+      </c>
+      <c r="AH402" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI402" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ402" t="s" s="2">
+        <v>1038</v>
+      </c>
+      <c r="AK402" t="s" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="s" s="2">
+        <v>1001</v>
+      </c>
+      <c r="B403" t="s" s="2">
+        <v>1106</v>
+      </c>
+      <c r="C403" t="s" s="2">
+        <v>1043</v>
+      </c>
+      <c r="D403" s="2"/>
+      <c r="E403" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="F403" s="2"/>
+      <c r="G403" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H403" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I403" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="J403" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="K403" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L403" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="M403" t="s" s="2">
+        <v>1044</v>
+      </c>
+      <c r="N403" t="s" s="2">
+        <v>1045</v>
+      </c>
+      <c r="O403" t="s" s="2">
+        <v>1046</v>
+      </c>
+      <c r="P403" s="2"/>
+      <c r="Q403" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="R403" s="2"/>
+      <c r="S403" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="T403" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="U403" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="V403" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="W403" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="X403" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Y403" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Z403" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AA403" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AB403" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AC403" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AD403" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AE403" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AF403" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AG403" t="s" s="2">
+        <v>1043</v>
+      </c>
+      <c r="AH403" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI403" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ403" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AK403" t="s" s="2">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="s" s="2">
+        <v>1001</v>
+      </c>
+      <c r="B404" t="s" s="2">
+        <v>1107</v>
+      </c>
+      <c r="C404" t="s" s="2">
+        <v>1022</v>
+      </c>
+      <c r="D404" t="s" s="2">
+        <v>1108</v>
+      </c>
+      <c r="E404" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="F404" s="2"/>
+      <c r="G404" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H404" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I404" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="J404" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="K404" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L404" t="s" s="2">
+        <v>722</v>
+      </c>
+      <c r="M404" t="s" s="2">
+        <v>1024</v>
+      </c>
+      <c r="N404" t="s" s="2">
+        <v>1025</v>
+      </c>
+      <c r="O404" s="2"/>
+      <c r="P404" s="2"/>
+      <c r="Q404" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="R404" s="2"/>
+      <c r="S404" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="T404" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="U404" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="V404" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="W404" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="X404" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Y404" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Z404" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AA404" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AB404" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AC404" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AD404" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AE404" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AF404" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AG404" t="s" s="2">
+        <v>1022</v>
+      </c>
+      <c r="AH404" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI404" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ404" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AK404" t="s" s="2">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="s" s="2">
+        <v>1001</v>
+      </c>
+      <c r="B405" t="s" s="2">
+        <v>1109</v>
+      </c>
+      <c r="C405" t="s" s="2">
+        <v>1029</v>
+      </c>
+      <c r="D405" s="2"/>
+      <c r="E405" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="F405" s="2"/>
+      <c r="G405" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H405" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I405" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="J405" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="K405" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="L405" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="M405" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="N405" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="O405" s="2"/>
+      <c r="P405" s="2"/>
+      <c r="Q405" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="R405" s="2"/>
+      <c r="S405" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="T405" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="U405" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="V405" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="W405" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="X405" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Y405" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Z405" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AA405" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AB405" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AC405" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AD405" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AE405" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AF405" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AG405" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AH405" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI405" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ405" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AK405" t="s" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="s" s="2">
+        <v>1001</v>
+      </c>
+      <c r="B406" t="s" s="2">
+        <v>1110</v>
+      </c>
+      <c r="C406" t="s" s="2">
+        <v>1030</v>
+      </c>
+      <c r="D406" s="2"/>
+      <c r="E406" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="F406" s="2"/>
+      <c r="G406" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H406" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I406" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="J406" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="K406" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="L406" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="M406" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="N406" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="O406" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="P406" s="2"/>
+      <c r="Q406" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="R406" s="2"/>
+      <c r="S406" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="T406" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="U406" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="V406" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="W406" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="X406" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Y406" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Z406" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AA406" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AB406" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AC406" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AD406" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AE406" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AF406" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AG406" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AH406" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI406" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ406" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AK406" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="s" s="2">
+        <v>1001</v>
+      </c>
+      <c r="B407" t="s" s="2">
+        <v>1111</v>
+      </c>
+      <c r="C407" t="s" s="2">
+        <v>1031</v>
+      </c>
+      <c r="D407" s="2"/>
+      <c r="E407" t="s" s="2">
+        <v>731</v>
+      </c>
+      <c r="F407" s="2"/>
+      <c r="G407" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H407" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I407" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="J407" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="K407" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L407" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="M407" t="s" s="2">
+        <v>732</v>
+      </c>
+      <c r="N407" t="s" s="2">
+        <v>733</v>
+      </c>
+      <c r="O407" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="P407" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="Q407" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="R407" s="2"/>
+      <c r="S407" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="T407" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="U407" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="V407" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="W407" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="X407" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Y407" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Z407" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AA407" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AB407" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AC407" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AD407" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AE407" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AF407" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AG407" t="s" s="2">
+        <v>734</v>
+      </c>
+      <c r="AH407" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI407" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ407" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AK407" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="s" s="2">
+        <v>1001</v>
+      </c>
+      <c r="B408" t="s" s="2">
+        <v>1112</v>
+      </c>
+      <c r="C408" t="s" s="2">
+        <v>1032</v>
+      </c>
+      <c r="D408" s="2"/>
+      <c r="E408" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="F408" s="2"/>
+      <c r="G408" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H408" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I408" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="J408" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="K408" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L408" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="M408" t="s" s="2">
+        <v>1033</v>
+      </c>
+      <c r="N408" t="s" s="2">
+        <v>1034</v>
+      </c>
+      <c r="O408" s="2"/>
+      <c r="P408" s="2"/>
+      <c r="Q408" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="R408" s="2"/>
+      <c r="S408" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="T408" t="s" s="2">
+        <v>1108</v>
+      </c>
+      <c r="U408" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="V408" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="W408" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="X408" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Y408" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Z408" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AA408" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AB408" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AC408" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AD408" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AE408" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AF408" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AG408" t="s" s="2">
+        <v>1032</v>
+      </c>
+      <c r="AH408" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI408" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ408" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AK408" t="s" s="2">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="s" s="2">
+        <v>1001</v>
+      </c>
+      <c r="B409" t="s" s="2">
+        <v>1113</v>
+      </c>
+      <c r="C409" t="s" s="2">
+        <v>1035</v>
+      </c>
+      <c r="D409" s="2"/>
+      <c r="E409" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="F409" s="2"/>
+      <c r="G409" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H409" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I409" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="J409" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="K409" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L409" t="s" s="2">
+        <v>1114</v>
+      </c>
+      <c r="M409" t="s" s="2">
+        <v>1036</v>
+      </c>
+      <c r="N409" t="s" s="2">
+        <v>1037</v>
+      </c>
+      <c r="O409" s="2"/>
+      <c r="P409" s="2"/>
+      <c r="Q409" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="R409" s="2"/>
+      <c r="S409" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="T409" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="U409" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="V409" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="W409" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="X409" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Y409" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Z409" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AA409" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AB409" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AC409" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AD409" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AE409" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AF409" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AG409" t="s" s="2">
+        <v>1035</v>
+      </c>
+      <c r="AH409" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI409" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ409" t="s" s="2">
+        <v>1038</v>
+      </c>
+      <c r="AK409" t="s" s="2">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="s" s="2">
+        <v>1001</v>
+      </c>
+      <c r="B410" t="s" s="2">
+        <v>1115</v>
+      </c>
+      <c r="C410" t="s" s="2">
+        <v>1039</v>
+      </c>
+      <c r="D410" s="2"/>
+      <c r="E410" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="F410" s="2"/>
+      <c r="G410" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H410" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I410" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="J410" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="K410" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L410" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="M410" t="s" s="2">
+        <v>1040</v>
+      </c>
+      <c r="N410" t="s" s="2">
+        <v>1041</v>
+      </c>
+      <c r="O410" t="s" s="2">
+        <v>1042</v>
+      </c>
+      <c r="P410" s="2"/>
+      <c r="Q410" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="R410" s="2"/>
+      <c r="S410" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="T410" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="U410" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="V410" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="W410" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="X410" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Y410" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Z410" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AA410" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AB410" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AC410" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AD410" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AE410" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AF410" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AG410" t="s" s="2">
+        <v>1039</v>
+      </c>
+      <c r="AH410" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI410" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ410" t="s" s="2">
+        <v>1038</v>
+      </c>
+      <c r="AK410" t="s" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="s" s="2">
+        <v>1001</v>
+      </c>
+      <c r="B411" t="s" s="2">
+        <v>1116</v>
+      </c>
+      <c r="C411" t="s" s="2">
+        <v>1043</v>
+      </c>
+      <c r="D411" s="2"/>
+      <c r="E411" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="F411" s="2"/>
+      <c r="G411" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H411" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I411" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="J411" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="K411" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L411" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="M411" t="s" s="2">
+        <v>1044</v>
+      </c>
+      <c r="N411" t="s" s="2">
+        <v>1045</v>
+      </c>
+      <c r="O411" t="s" s="2">
+        <v>1046</v>
+      </c>
+      <c r="P411" s="2"/>
+      <c r="Q411" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="R411" s="2"/>
+      <c r="S411" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="T411" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="U411" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="V411" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="W411" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="X411" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Y411" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Z411" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AA411" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AB411" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AC411" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AD411" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AE411" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AF411" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AG411" t="s" s="2">
+        <v>1043</v>
+      </c>
+      <c r="AH411" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI411" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ411" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AK411" t="s" s="2">
+        <v>121</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/main/all-profiles.xlsx
+++ b/main/all-profiles.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13706" uniqueCount="1117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13444" uniqueCount="1108">
   <si>
     <t>Property</t>
   </si>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-05</t>
+    <t>2026-09-16</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -3176,7 +3176,7 @@
     <t>Parameters.parameter</t>
   </si>
   <si>
-    <t>8</t>
+    <t>7</t>
   </si>
   <si>
     <t>Operation Parameter</t>
@@ -3285,62 +3285,35 @@
     <t>Parameters.parameter:matchItem.part</t>
   </si>
   <si>
-    <t>Parameters.parameter:matchScore</t>
-  </si>
-  <si>
-    <t>matchScore</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:matchScore.id</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:matchScore.extension</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:matchScore.modifierExtension</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:matchScore.name</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:matchScore.value[x]</t>
+    <t>Parameters.parameter:matchProbability</t>
+  </si>
+  <si>
+    <t>matchProbability</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:matchProbability.id</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:matchProbability.extension</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:matchProbability.modifierExtension</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:matchProbability.name</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:matchProbability.value[x]</t>
   </si>
   <si>
     <t xml:space="preserve">decimal
 </t>
   </si>
   <si>
-    <t>Parameters.parameter:matchScore.resource</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:matchScore.part</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:matchResult</t>
-  </si>
-  <si>
-    <t>matchResult</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:matchResult.id</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:matchResult.extension</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:matchResult.modifierExtension</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:matchResult.name</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:matchResult.value[x]</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:matchResult.resource</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:matchResult.part</t>
+    <t>Parameters.parameter:matchProbability.resource</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:matchProbability.part</t>
   </si>
   <si>
     <t>Parameters.parameter:matchCreated</t>
@@ -4290,7 +4263,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK411"/>
+  <dimension ref="A1:AK403"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="21.1171875" customWidth="true" bestFit="true"/>
@@ -43743,7 +43716,7 @@
         <v>101</v>
       </c>
       <c r="L377" t="s" s="2">
-        <v>1065</v>
+        <v>1075</v>
       </c>
       <c r="M377" t="s" s="2">
         <v>1036</v>
@@ -43820,7 +43793,7 @@
         <v>1001</v>
       </c>
       <c r="B378" t="s" s="2">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="C378" t="s" s="2">
         <v>1039</v>
@@ -43925,7 +43898,7 @@
         <v>1001</v>
       </c>
       <c r="B379" t="s" s="2">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="C379" t="s" s="2">
         <v>1043</v>
@@ -44030,13 +44003,13 @@
         <v>1001</v>
       </c>
       <c r="B380" t="s" s="2">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="C380" t="s" s="2">
         <v>1022</v>
       </c>
       <c r="D380" t="s" s="2">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="E380" t="s" s="2">
         <v>22</v>
@@ -44135,7 +44108,7 @@
         <v>1001</v>
       </c>
       <c r="B381" t="s" s="2">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="C381" t="s" s="2">
         <v>1029</v>
@@ -44238,7 +44211,7 @@
         <v>1001</v>
       </c>
       <c r="B382" t="s" s="2">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="C382" t="s" s="2">
         <v>1030</v>
@@ -44343,7 +44316,7 @@
         <v>1001</v>
       </c>
       <c r="B383" t="s" s="2">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="C383" t="s" s="2">
         <v>1031</v>
@@ -44450,7 +44423,7 @@
         <v>1001</v>
       </c>
       <c r="B384" t="s" s="2">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="C384" t="s" s="2">
         <v>1032</v>
@@ -44494,7 +44467,7 @@
         <v>22</v>
       </c>
       <c r="T384" t="s" s="2">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="U384" t="s" s="2">
         <v>22</v>
@@ -44553,7 +44526,7 @@
         <v>1001</v>
       </c>
       <c r="B385" t="s" s="2">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="C385" t="s" s="2">
         <v>1035</v>
@@ -44579,7 +44552,7 @@
         <v>101</v>
       </c>
       <c r="L385" t="s" s="2">
-        <v>1084</v>
+        <v>390</v>
       </c>
       <c r="M385" t="s" s="2">
         <v>1036</v>
@@ -44612,13 +44585,11 @@
         <v>22</v>
       </c>
       <c r="Y385" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="Z385" t="s" s="2">
-        <v>22</v>
-      </c>
+        <v>304</v>
+      </c>
+      <c r="Z385" s="2"/>
       <c r="AA385" t="s" s="2">
-        <v>22</v>
+        <v>1085</v>
       </c>
       <c r="AB385" t="s" s="2">
         <v>22</v>
@@ -44656,7 +44627,7 @@
         <v>1001</v>
       </c>
       <c r="B386" t="s" s="2">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="C386" t="s" s="2">
         <v>1039</v>
@@ -44761,7 +44732,7 @@
         <v>1001</v>
       </c>
       <c r="B387" t="s" s="2">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="C387" t="s" s="2">
         <v>1043</v>
@@ -44866,13 +44837,13 @@
         <v>1001</v>
       </c>
       <c r="B388" t="s" s="2">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="C388" t="s" s="2">
         <v>1022</v>
       </c>
       <c r="D388" t="s" s="2">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="E388" t="s" s="2">
         <v>22</v>
@@ -44971,7 +44942,7 @@
         <v>1001</v>
       </c>
       <c r="B389" t="s" s="2">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="C389" t="s" s="2">
         <v>1029</v>
@@ -45074,7 +45045,7 @@
         <v>1001</v>
       </c>
       <c r="B390" t="s" s="2">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="C390" t="s" s="2">
         <v>1030</v>
@@ -45179,7 +45150,7 @@
         <v>1001</v>
       </c>
       <c r="B391" t="s" s="2">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="C391" t="s" s="2">
         <v>1031</v>
@@ -45286,7 +45257,7 @@
         <v>1001</v>
       </c>
       <c r="B392" t="s" s="2">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="C392" t="s" s="2">
         <v>1032</v>
@@ -45330,7 +45301,7 @@
         <v>22</v>
       </c>
       <c r="T392" t="s" s="2">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="U392" t="s" s="2">
         <v>22</v>
@@ -45389,7 +45360,7 @@
         <v>1001</v>
       </c>
       <c r="B393" t="s" s="2">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="C393" t="s" s="2">
         <v>1035</v>
@@ -45452,7 +45423,7 @@
       </c>
       <c r="Z393" s="2"/>
       <c r="AA393" t="s" s="2">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="AB393" t="s" s="2">
         <v>22</v>
@@ -45490,7 +45461,7 @@
         <v>1001</v>
       </c>
       <c r="B394" t="s" s="2">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="C394" t="s" s="2">
         <v>1039</v>
@@ -45595,7 +45566,7 @@
         <v>1001</v>
       </c>
       <c r="B395" t="s" s="2">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="C395" t="s" s="2">
         <v>1043</v>
@@ -45700,13 +45671,13 @@
         <v>1001</v>
       </c>
       <c r="B396" t="s" s="2">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="C396" t="s" s="2">
         <v>1022</v>
       </c>
       <c r="D396" t="s" s="2">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="E396" t="s" s="2">
         <v>22</v>
@@ -45805,7 +45776,7 @@
         <v>1001</v>
       </c>
       <c r="B397" t="s" s="2">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="C397" t="s" s="2">
         <v>1029</v>
@@ -45908,7 +45879,7 @@
         <v>1001</v>
       </c>
       <c r="B398" t="s" s="2">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="C398" t="s" s="2">
         <v>1030</v>
@@ -46013,7 +45984,7 @@
         <v>1001</v>
       </c>
       <c r="B399" t="s" s="2">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="C399" t="s" s="2">
         <v>1031</v>
@@ -46120,7 +46091,7 @@
         <v>1001</v>
       </c>
       <c r="B400" t="s" s="2">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="C400" t="s" s="2">
         <v>1032</v>
@@ -46164,7 +46135,7 @@
         <v>22</v>
       </c>
       <c r="T400" t="s" s="2">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="U400" t="s" s="2">
         <v>22</v>
@@ -46223,7 +46194,7 @@
         <v>1001</v>
       </c>
       <c r="B401" t="s" s="2">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="C401" t="s" s="2">
         <v>1035</v>
@@ -46249,7 +46220,7 @@
         <v>101</v>
       </c>
       <c r="L401" t="s" s="2">
-        <v>390</v>
+        <v>1105</v>
       </c>
       <c r="M401" t="s" s="2">
         <v>1036</v>
@@ -46282,11 +46253,13 @@
         <v>22</v>
       </c>
       <c r="Y401" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="Z401" s="2"/>
+        <v>22</v>
+      </c>
+      <c r="Z401" t="s" s="2">
+        <v>22</v>
+      </c>
       <c r="AA401" t="s" s="2">
-        <v>1104</v>
+        <v>22</v>
       </c>
       <c r="AB401" t="s" s="2">
         <v>22</v>
@@ -46324,7 +46297,7 @@
         <v>1001</v>
       </c>
       <c r="B402" t="s" s="2">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="C402" t="s" s="2">
         <v>1039</v>
@@ -46429,7 +46402,7 @@
         <v>1001</v>
       </c>
       <c r="B403" t="s" s="2">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="C403" t="s" s="2">
         <v>1043</v>
@@ -46526,842 +46499,6 @@
         <v>22</v>
       </c>
       <c r="AK403" t="s" s="2">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="404">
-      <c r="A404" t="s" s="2">
-        <v>1001</v>
-      </c>
-      <c r="B404" t="s" s="2">
-        <v>1107</v>
-      </c>
-      <c r="C404" t="s" s="2">
-        <v>1022</v>
-      </c>
-      <c r="D404" t="s" s="2">
-        <v>1108</v>
-      </c>
-      <c r="E404" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="F404" s="2"/>
-      <c r="G404" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="H404" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I404" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="J404" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="K404" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="L404" t="s" s="2">
-        <v>722</v>
-      </c>
-      <c r="M404" t="s" s="2">
-        <v>1024</v>
-      </c>
-      <c r="N404" t="s" s="2">
-        <v>1025</v>
-      </c>
-      <c r="O404" s="2"/>
-      <c r="P404" s="2"/>
-      <c r="Q404" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="R404" s="2"/>
-      <c r="S404" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="T404" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="U404" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="V404" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="W404" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="X404" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="Y404" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="Z404" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AA404" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AB404" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AC404" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AD404" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AE404" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AF404" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AG404" t="s" s="2">
-        <v>1022</v>
-      </c>
-      <c r="AH404" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI404" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ404" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AK404" t="s" s="2">
-        <v>1028</v>
-      </c>
-    </row>
-    <row r="405">
-      <c r="A405" t="s" s="2">
-        <v>1001</v>
-      </c>
-      <c r="B405" t="s" s="2">
-        <v>1109</v>
-      </c>
-      <c r="C405" t="s" s="2">
-        <v>1029</v>
-      </c>
-      <c r="D405" s="2"/>
-      <c r="E405" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="F405" s="2"/>
-      <c r="G405" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H405" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I405" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="J405" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="K405" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="L405" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="M405" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="N405" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="O405" s="2"/>
-      <c r="P405" s="2"/>
-      <c r="Q405" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="R405" s="2"/>
-      <c r="S405" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="T405" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="U405" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="V405" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="W405" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="X405" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="Y405" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="Z405" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AA405" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AB405" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AC405" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AD405" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AE405" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AF405" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AG405" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AH405" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI405" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ405" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AK405" t="s" s="2">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="406">
-      <c r="A406" t="s" s="2">
-        <v>1001</v>
-      </c>
-      <c r="B406" t="s" s="2">
-        <v>1110</v>
-      </c>
-      <c r="C406" t="s" s="2">
-        <v>1030</v>
-      </c>
-      <c r="D406" s="2"/>
-      <c r="E406" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="F406" s="2"/>
-      <c r="G406" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H406" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I406" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="J406" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="K406" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="L406" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="M406" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="N406" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="O406" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="P406" s="2"/>
-      <c r="Q406" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="R406" s="2"/>
-      <c r="S406" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="T406" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="U406" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="V406" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="W406" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="X406" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="Y406" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="Z406" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AA406" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AB406" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AC406" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AD406" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AE406" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AF406" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AG406" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="AH406" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI406" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ406" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AK406" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="407">
-      <c r="A407" t="s" s="2">
-        <v>1001</v>
-      </c>
-      <c r="B407" t="s" s="2">
-        <v>1111</v>
-      </c>
-      <c r="C407" t="s" s="2">
-        <v>1031</v>
-      </c>
-      <c r="D407" s="2"/>
-      <c r="E407" t="s" s="2">
-        <v>731</v>
-      </c>
-      <c r="F407" s="2"/>
-      <c r="G407" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H407" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I407" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="J407" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="K407" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="L407" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="M407" t="s" s="2">
-        <v>732</v>
-      </c>
-      <c r="N407" t="s" s="2">
-        <v>733</v>
-      </c>
-      <c r="O407" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="P407" t="s" s="2">
-        <v>466</v>
-      </c>
-      <c r="Q407" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="R407" s="2"/>
-      <c r="S407" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="T407" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="U407" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="V407" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="W407" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="X407" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="Y407" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="Z407" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AA407" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AB407" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AC407" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AD407" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AE407" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AF407" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AG407" t="s" s="2">
-        <v>734</v>
-      </c>
-      <c r="AH407" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI407" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ407" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AK407" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="408">
-      <c r="A408" t="s" s="2">
-        <v>1001</v>
-      </c>
-      <c r="B408" t="s" s="2">
-        <v>1112</v>
-      </c>
-      <c r="C408" t="s" s="2">
-        <v>1032</v>
-      </c>
-      <c r="D408" s="2"/>
-      <c r="E408" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="F408" s="2"/>
-      <c r="G408" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="H408" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I408" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="J408" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="K408" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="L408" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="M408" t="s" s="2">
-        <v>1033</v>
-      </c>
-      <c r="N408" t="s" s="2">
-        <v>1034</v>
-      </c>
-      <c r="O408" s="2"/>
-      <c r="P408" s="2"/>
-      <c r="Q408" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="R408" s="2"/>
-      <c r="S408" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="T408" t="s" s="2">
-        <v>1108</v>
-      </c>
-      <c r="U408" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="V408" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="W408" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="X408" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="Y408" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="Z408" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AA408" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AB408" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AC408" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AD408" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AE408" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AF408" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AG408" t="s" s="2">
-        <v>1032</v>
-      </c>
-      <c r="AH408" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI408" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ408" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AK408" t="s" s="2">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="409">
-      <c r="A409" t="s" s="2">
-        <v>1001</v>
-      </c>
-      <c r="B409" t="s" s="2">
-        <v>1113</v>
-      </c>
-      <c r="C409" t="s" s="2">
-        <v>1035</v>
-      </c>
-      <c r="D409" s="2"/>
-      <c r="E409" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="F409" s="2"/>
-      <c r="G409" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="H409" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I409" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="J409" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="K409" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="L409" t="s" s="2">
-        <v>1114</v>
-      </c>
-      <c r="M409" t="s" s="2">
-        <v>1036</v>
-      </c>
-      <c r="N409" t="s" s="2">
-        <v>1037</v>
-      </c>
-      <c r="O409" s="2"/>
-      <c r="P409" s="2"/>
-      <c r="Q409" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="R409" s="2"/>
-      <c r="S409" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="T409" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="U409" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="V409" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="W409" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="X409" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="Y409" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="Z409" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AA409" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AB409" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AC409" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AD409" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AE409" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AF409" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AG409" t="s" s="2">
-        <v>1035</v>
-      </c>
-      <c r="AH409" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI409" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ409" t="s" s="2">
-        <v>1038</v>
-      </c>
-      <c r="AK409" t="s" s="2">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="410">
-      <c r="A410" t="s" s="2">
-        <v>1001</v>
-      </c>
-      <c r="B410" t="s" s="2">
-        <v>1115</v>
-      </c>
-      <c r="C410" t="s" s="2">
-        <v>1039</v>
-      </c>
-      <c r="D410" s="2"/>
-      <c r="E410" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="F410" s="2"/>
-      <c r="G410" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H410" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I410" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="J410" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="K410" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="L410" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="M410" t="s" s="2">
-        <v>1040</v>
-      </c>
-      <c r="N410" t="s" s="2">
-        <v>1041</v>
-      </c>
-      <c r="O410" t="s" s="2">
-        <v>1042</v>
-      </c>
-      <c r="P410" s="2"/>
-      <c r="Q410" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="R410" s="2"/>
-      <c r="S410" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="T410" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="U410" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="V410" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="W410" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="X410" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="Y410" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="Z410" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AA410" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AB410" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AC410" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AD410" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AE410" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AF410" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AG410" t="s" s="2">
-        <v>1039</v>
-      </c>
-      <c r="AH410" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI410" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ410" t="s" s="2">
-        <v>1038</v>
-      </c>
-      <c r="AK410" t="s" s="2">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="411">
-      <c r="A411" t="s" s="2">
-        <v>1001</v>
-      </c>
-      <c r="B411" t="s" s="2">
-        <v>1116</v>
-      </c>
-      <c r="C411" t="s" s="2">
-        <v>1043</v>
-      </c>
-      <c r="D411" s="2"/>
-      <c r="E411" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="F411" s="2"/>
-      <c r="G411" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H411" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I411" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="J411" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="K411" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="L411" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="M411" t="s" s="2">
-        <v>1044</v>
-      </c>
-      <c r="N411" t="s" s="2">
-        <v>1045</v>
-      </c>
-      <c r="O411" t="s" s="2">
-        <v>1046</v>
-      </c>
-      <c r="P411" s="2"/>
-      <c r="Q411" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="R411" s="2"/>
-      <c r="S411" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="T411" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="U411" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="V411" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="W411" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="X411" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="Y411" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="Z411" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AA411" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AB411" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AC411" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AD411" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AE411" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AF411" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AG411" t="s" s="2">
-        <v>1043</v>
-      </c>
-      <c r="AH411" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI411" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ411" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AK411" t="s" s="2">
         <v>121</v>
       </c>
     </row>

--- a/main/all-profiles.xlsx
+++ b/main/all-profiles.xlsx
@@ -3407,35 +3407,35 @@
     <t>Parameters.parameter:matchPriority.part</t>
   </si>
   <si>
-    <t>Parameters.parameter:linkId</t>
-  </si>
-  <si>
-    <t>linkId</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:linkId.id</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:linkId.extension</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:linkId.modifierExtension</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:linkId.name</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:linkId.value[x]</t>
+    <t>Parameters.parameter:matchLinkId</t>
+  </si>
+  <si>
+    <t>matchLinkId</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:matchLinkId.id</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:matchLinkId.extension</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:matchLinkId.modifierExtension</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:matchLinkId.name</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:matchLinkId.value[x]</t>
   </si>
   <si>
     <t xml:space="preserve">integer
 </t>
   </si>
   <si>
-    <t>Parameters.parameter:linkId.resource</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:linkId.part</t>
+    <t>Parameters.parameter:matchLinkId.resource</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:matchLinkId.part</t>
   </si>
 </sst>
 </file>
